--- a/scorecard/scorecard_data/final/index_scores_wide_tableau_excel.xlsx
+++ b/scorecard/scorecard_data/final/index_scores_wide_tableau_excel.xlsx
@@ -1697,7 +1697,9 @@
     <col min="20" max="20" width="29.1719" style="1" customWidth="1"/>
     <col min="21" max="24" width="17.6719" style="1" customWidth="1"/>
     <col min="25" max="25" width="22" style="1" customWidth="1"/>
-    <col min="26" max="29" width="17.6719" style="1" customWidth="1"/>
+    <col min="26" max="26" width="17.6719" style="1" customWidth="1"/>
+    <col min="27" max="27" width="18.6719" style="1" customWidth="1"/>
+    <col min="28" max="29" width="17.6719" style="1" customWidth="1"/>
     <col min="30" max="16384" width="8.35156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1834,82 +1836,82 @@
         <v>31</v>
       </c>
       <c r="D3" s="7">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E3" s="7">
-        <v>36.7129109588447</v>
+        <v>41.0773371628743</v>
       </c>
       <c r="F3" s="7">
-        <v>58.4419086234759</v>
+        <v>65.7770452822342</v>
       </c>
       <c r="G3" s="7">
-        <v>14.9839132942134</v>
+        <v>16.3776290435144</v>
       </c>
       <c r="H3" s="7">
-        <v>62.3961352271291</v>
+        <v>61.1567888270988</v>
       </c>
       <c r="I3" s="7">
-        <v>64.03666809855071</v>
+        <v>56.5361570742934</v>
       </c>
       <c r="J3" s="7">
-        <v>52.0893356657171</v>
+        <v>52.3886304882715</v>
       </c>
       <c r="K3" s="7">
-        <v>36.2821277984947</v>
+        <v>38.5259584000763</v>
       </c>
       <c r="L3" s="7">
         <v>97.176409345754</v>
       </c>
       <c r="M3" s="7">
-        <v>44.7807704060433</v>
+        <v>47.3161088755477</v>
       </c>
       <c r="N3" s="7">
-        <v>58.8887886919624</v>
+        <v>59.288871461099</v>
       </c>
       <c r="O3" s="7">
-        <v>30.6727521201241</v>
+        <v>35.3433462899964</v>
       </c>
       <c r="P3" s="7">
-        <v>47.963272197339</v>
+        <v>49.8500782885069</v>
       </c>
       <c r="Q3" s="7">
-        <v>59.5511932561076</v>
+        <v>55.184479954798</v>
       </c>
       <c r="R3" s="7">
-        <v>44.1114510353227</v>
+        <v>36.3804213840751</v>
       </c>
       <c r="S3" s="7">
-        <v>74.9909354768926</v>
+        <v>73.98853852552089</v>
       </c>
       <c r="T3" s="7">
-        <v>57.3017368438698</v>
+        <v>58.0357315037395</v>
       </c>
       <c r="U3" s="7">
-        <v>56.8349119239335</v>
+        <v>55.5020747877113</v>
       </c>
       <c r="V3" s="7">
-        <v>57.807235103210</v>
+        <v>56.9219253023301</v>
       </c>
       <c r="W3" s="7">
-        <v>27.785985794608</v>
+        <v>32.9401113711892</v>
       </c>
       <c r="X3" s="7">
         <v>86.7788145537275</v>
       </c>
       <c r="Y3" s="7">
-        <v>74.10690202243561</v>
+        <v>74.2510981485639</v>
       </c>
       <c r="Z3" s="7">
-        <v>67.3521630361588</v>
+        <v>67.7999716310573</v>
       </c>
       <c r="AA3" s="7">
-        <v>80.8616410087124</v>
+        <v>80.70222466607051</v>
       </c>
       <c r="AB3" s="7">
-        <v>63.6532773741377</v>
+        <v>62.4904365357005</v>
       </c>
       <c r="AC3" s="7">
-        <v>55.8082747857383</v>
+        <v>56.1702574121037</v>
       </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
@@ -1923,82 +1925,82 @@
         <v>33</v>
       </c>
       <c r="D4" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E4" s="11">
-        <v>53.1901204319654</v>
+        <v>51.2247027816099</v>
       </c>
       <c r="F4" s="11">
-        <v>43.7619241730897</v>
+        <v>46.1709953127595</v>
       </c>
       <c r="G4" s="11">
-        <v>62.618316690841</v>
+        <v>56.2784102504603</v>
       </c>
       <c r="H4" s="11">
-        <v>58.1099488874551</v>
+        <v>59.380876691005</v>
       </c>
       <c r="I4" s="11">
-        <v>41.6874481901385</v>
+        <v>48.0563785025574</v>
       </c>
       <c r="J4" s="11">
-        <v>78.7327785156193</v>
+        <v>77.26403912223449</v>
       </c>
       <c r="K4" s="11">
-        <v>50.0623785578252</v>
+        <v>50.2458988529909</v>
       </c>
       <c r="L4" s="11">
         <v>61.9571902862374</v>
       </c>
       <c r="M4" s="11">
-        <v>56.7398848759633</v>
+        <v>58.5474427574418</v>
       </c>
       <c r="N4" s="11">
-        <v>59.512158418068</v>
+        <v>56.3544329669479</v>
       </c>
       <c r="O4" s="11">
-        <v>53.9676113338587</v>
+        <v>60.7404525479357</v>
       </c>
       <c r="P4" s="11">
-        <v>56.0133180651279</v>
+        <v>56.3843407433523</v>
       </c>
       <c r="Q4" s="11">
-        <v>57.580846780231</v>
+        <v>60.8341504925734</v>
       </c>
       <c r="R4" s="11">
-        <v>79.8242400270601</v>
+        <v>81.9931982482202</v>
       </c>
       <c r="S4" s="11">
-        <v>35.3374535334018</v>
+        <v>39.6751027369266</v>
       </c>
       <c r="T4" s="11">
-        <v>30.3162268232811</v>
+        <v>30.6492822014122</v>
       </c>
       <c r="U4" s="11">
-        <v>17.236362690035</v>
+        <v>17.3482356376006</v>
       </c>
       <c r="V4" s="11">
-        <v>16.2089265340346</v>
+        <v>16.5782462445319</v>
       </c>
       <c r="W4" s="11">
-        <v>52.3132873167425</v>
+        <v>53.164316171204</v>
       </c>
       <c r="X4" s="11">
         <v>35.5063307523124</v>
       </c>
       <c r="Y4" s="11">
-        <v>22.2920941963093</v>
+        <v>22.8680020213349</v>
       </c>
       <c r="Z4" s="11">
-        <v>9.50616872602774</v>
+        <v>9.432057117032411</v>
       </c>
       <c r="AA4" s="11">
-        <v>35.0780196665908</v>
+        <v>36.3039469256373</v>
       </c>
       <c r="AB4" s="11">
-        <v>36.7297225999405</v>
+        <v>38.1171449051068</v>
       </c>
       <c r="AC4" s="11">
-        <v>46.3715203325342</v>
+        <v>47.2507428242295</v>
       </c>
     </row>
     <row r="5" ht="20.05" customHeight="1">
@@ -2012,82 +2014,82 @@
         <v>35</v>
       </c>
       <c r="D5" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E5" s="11">
-        <v>38.8835116820458</v>
+        <v>39.4131808106401</v>
       </c>
       <c r="F5" s="11">
-        <v>49.7880743054963</v>
+        <v>51.3969653267847</v>
       </c>
       <c r="G5" s="11">
-        <v>27.9789490585952</v>
+        <v>27.4293962944955</v>
       </c>
       <c r="H5" s="11">
-        <v>49.4714861182524</v>
+        <v>49.0469263770933</v>
       </c>
       <c r="I5" s="11">
-        <v>43.826344273559</v>
+        <v>43.1339372388043</v>
       </c>
       <c r="J5" s="11">
-        <v>65.051045409655</v>
+        <v>65.1310362928654</v>
       </c>
       <c r="K5" s="11">
-        <v>32.5807637430426</v>
+        <v>31.4949409299503</v>
       </c>
       <c r="L5" s="11">
         <v>56.4277910467531</v>
       </c>
       <c r="M5" s="11">
-        <v>66.4812154893842</v>
+        <v>64.5342040907321</v>
       </c>
       <c r="N5" s="11">
-        <v>57.194885168377</v>
+        <v>55.0040663633749</v>
       </c>
       <c r="O5" s="11">
-        <v>75.7675458103914</v>
+        <v>74.0643418180893</v>
       </c>
       <c r="P5" s="11">
-        <v>51.6120710965608</v>
+        <v>50.9981037594885</v>
       </c>
       <c r="Q5" s="11">
-        <v>74.4647884667415</v>
+        <v>74.6615931993399</v>
       </c>
       <c r="R5" s="11">
-        <v>87.94608968954979</v>
+        <v>86.8863434962839</v>
       </c>
       <c r="S5" s="11">
-        <v>60.9834872439332</v>
+        <v>62.4368429023959</v>
       </c>
       <c r="T5" s="11">
-        <v>32.5077953417455</v>
+        <v>32.6919977633003</v>
       </c>
       <c r="U5" s="11">
-        <v>19.1849698437032</v>
+        <v>20.3760395894939</v>
       </c>
       <c r="V5" s="11">
-        <v>18.9221162228165</v>
+        <v>17.6064119921272</v>
       </c>
       <c r="W5" s="11">
-        <v>57.318160086520</v>
+        <v>58.1796042576378</v>
       </c>
       <c r="X5" s="11">
         <v>34.6059352139421</v>
       </c>
       <c r="Y5" s="11">
-        <v>18.4798745291002</v>
+        <v>18.2141603646208</v>
       </c>
       <c r="Z5" s="11">
-        <v>10.0310471668664</v>
+        <v>9.363992945596181</v>
       </c>
       <c r="AA5" s="11">
-        <v>26.9287018913341</v>
+        <v>27.0643277836455</v>
       </c>
       <c r="AB5" s="11">
-        <v>41.8174861125291</v>
+        <v>41.855917109087</v>
       </c>
       <c r="AC5" s="11">
-        <v>46.7147786045449</v>
+        <v>46.4270104342877</v>
       </c>
     </row>
     <row r="6" ht="20.05" customHeight="1">
@@ -2101,82 +2103,82 @@
         <v>37</v>
       </c>
       <c r="D6" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E6" s="11">
-        <v>48.0904821611305</v>
+        <v>46.4961698517481</v>
       </c>
       <c r="F6" s="11">
-        <v>72.6403816374696</v>
+        <v>71.534112485891</v>
       </c>
       <c r="G6" s="11">
-        <v>23.5405826847914</v>
+        <v>21.4582272176052</v>
       </c>
       <c r="H6" s="11">
-        <v>56.2173703740342</v>
+        <v>53.9275702696057</v>
       </c>
       <c r="I6" s="11">
-        <v>35.4961712793798</v>
+        <v>27.5655372892251</v>
       </c>
       <c r="J6" s="11">
-        <v>50.425520262252</v>
+        <v>49.5031743836529</v>
       </c>
       <c r="K6" s="11">
-        <v>46.794453648514</v>
+        <v>46.4882330995542</v>
       </c>
       <c r="L6" s="11">
         <v>92.1533363059909</v>
       </c>
       <c r="M6" s="11">
-        <v>45.8621094347695</v>
+        <v>45.3800196395671</v>
       </c>
       <c r="N6" s="11">
-        <v>48.949485801674</v>
+        <v>49.6601381776117</v>
       </c>
       <c r="O6" s="11">
-        <v>42.774733067865</v>
+        <v>41.0999011015225</v>
       </c>
       <c r="P6" s="11">
-        <v>50.0566539899781</v>
+        <v>48.6012532536403</v>
       </c>
       <c r="Q6" s="11">
-        <v>65.96354650226981</v>
+        <v>68.0697382694381</v>
       </c>
       <c r="R6" s="11">
-        <v>73.35259086716751</v>
+        <v>73.81563777976341</v>
       </c>
       <c r="S6" s="11">
-        <v>58.5745021373721</v>
+        <v>62.3238387591127</v>
       </c>
       <c r="T6" s="11">
-        <v>60.5528135594746</v>
+        <v>60.1695026878685</v>
       </c>
       <c r="U6" s="11">
-        <v>55.4019668454051</v>
+        <v>55.5020747877113</v>
       </c>
       <c r="V6" s="11">
-        <v>61.5465750735817</v>
+        <v>61.7194624676191</v>
       </c>
       <c r="W6" s="11">
-        <v>37.0625954914492</v>
+        <v>35.2563566686812</v>
       </c>
       <c r="X6" s="11">
         <v>88.20011682746259</v>
       </c>
       <c r="Y6" s="11">
-        <v>60.8750601927727</v>
+        <v>63.4927999709401</v>
       </c>
       <c r="Z6" s="11">
-        <v>59.4888762925416</v>
+        <v>60.639947846168</v>
       </c>
       <c r="AA6" s="11">
-        <v>62.2612440930039</v>
+        <v>66.3456520957121</v>
       </c>
       <c r="AB6" s="11">
-        <v>62.4638067515057</v>
+        <v>63.9106803094156</v>
       </c>
       <c r="AC6" s="11">
-        <v>56.2602303707419</v>
+        <v>56.2559667815279</v>
       </c>
     </row>
     <row r="7" ht="20.05" customHeight="1">
@@ -2190,82 +2192,82 @@
         <v>39</v>
       </c>
       <c r="D7" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E7" s="11">
-        <v>55.4460116332382</v>
+        <v>55.039717891651</v>
       </c>
       <c r="F7" s="11">
-        <v>62.9361340511766</v>
+        <v>64.8440439110158</v>
       </c>
       <c r="G7" s="11">
-        <v>47.9558892152999</v>
+        <v>45.2353918722862</v>
       </c>
       <c r="H7" s="11">
-        <v>48.6050514048746</v>
+        <v>50.6078989560907</v>
       </c>
       <c r="I7" s="11">
-        <v>46.817514011081</v>
+        <v>51.5736334083425</v>
       </c>
       <c r="J7" s="11">
-        <v>60.5081183841201</v>
+        <v>62.9187527460972</v>
       </c>
       <c r="K7" s="11">
-        <v>41.4752178099972</v>
+        <v>42.3198542556229</v>
       </c>
       <c r="L7" s="11">
         <v>45.6193554143</v>
       </c>
       <c r="M7" s="11">
-        <v>27.0490580647686</v>
+        <v>26.6772734822108</v>
       </c>
       <c r="N7" s="11">
-        <v>14.2628156738475</v>
+        <v>13.4469528319042</v>
       </c>
       <c r="O7" s="11">
-        <v>39.8353004556897</v>
+        <v>39.9075941325174</v>
       </c>
       <c r="P7" s="11">
-        <v>43.7000403676271</v>
+        <v>44.1082967766508</v>
       </c>
       <c r="Q7" s="11">
-        <v>40.5648168790478</v>
+        <v>43.3549500757147</v>
       </c>
       <c r="R7" s="11">
-        <v>22.0858298246852</v>
+        <v>25.4223586992638</v>
       </c>
       <c r="S7" s="11">
-        <v>59.0438039334103</v>
+        <v>61.2875414521656</v>
       </c>
       <c r="T7" s="11">
-        <v>50.0647693492513</v>
+        <v>49.3057081887264</v>
       </c>
       <c r="U7" s="11">
-        <v>67.81307113777849</v>
+        <v>66.0891565918544</v>
       </c>
       <c r="V7" s="11">
-        <v>38.5026574319224</v>
+        <v>36.6131807189492</v>
       </c>
       <c r="W7" s="11">
-        <v>32.3687767602586</v>
+        <v>32.9459233770565</v>
       </c>
       <c r="X7" s="11">
         <v>61.5745720670456</v>
       </c>
       <c r="Y7" s="11">
-        <v>55.2884105034282</v>
+        <v>54.4418795638792</v>
       </c>
       <c r="Z7" s="11">
-        <v>43.0867770871742</v>
+        <v>41.5204563482206</v>
       </c>
       <c r="AA7" s="11">
-        <v>67.49004391968229</v>
+        <v>67.3633027795379</v>
       </c>
       <c r="AB7" s="11">
-        <v>48.6393322439091</v>
+        <v>49.0341792761068</v>
       </c>
       <c r="AC7" s="11">
-        <v>46.1696863057681</v>
+        <v>46.5712380263788</v>
       </c>
     </row>
     <row r="8" ht="20.05" customHeight="1">
@@ -2279,82 +2281,82 @@
         <v>41</v>
       </c>
       <c r="D8" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E8" s="11">
-        <v>56.6939404016003</v>
+        <v>56.475986810557</v>
       </c>
       <c r="F8" s="11">
-        <v>48.7857514893051</v>
+        <v>49.3396213599888</v>
       </c>
       <c r="G8" s="11">
-        <v>64.6021293138955</v>
+        <v>63.6123522611252</v>
       </c>
       <c r="H8" s="11">
-        <v>52.5513265820261</v>
+        <v>51.8653855546863</v>
       </c>
       <c r="I8" s="11">
-        <v>71.61330106463311</v>
+        <v>72.2864144970797</v>
       </c>
       <c r="J8" s="11">
-        <v>25.0088223235734</v>
+        <v>24.1032895296921</v>
       </c>
       <c r="K8" s="11">
-        <v>63.217819146121</v>
+        <v>60.7064743981965</v>
       </c>
       <c r="L8" s="11">
         <v>50.3653637937768</v>
       </c>
       <c r="M8" s="11">
-        <v>33.9587917444611</v>
+        <v>34.3329681413593</v>
       </c>
       <c r="N8" s="11">
-        <v>49.2841931705586</v>
+        <v>50.4646653542754</v>
       </c>
       <c r="O8" s="11">
-        <v>18.6333903183636</v>
+        <v>18.2012709284433</v>
       </c>
       <c r="P8" s="11">
-        <v>47.7346862426958</v>
+        <v>47.5581135022009</v>
       </c>
       <c r="Q8" s="11">
-        <v>45.6592036811309</v>
+        <v>45.0201591576295</v>
       </c>
       <c r="R8" s="11">
-        <v>55.3613581393748</v>
+        <v>52.8450846730781</v>
       </c>
       <c r="S8" s="11">
-        <v>35.957049222887</v>
+        <v>37.1952336421809</v>
       </c>
       <c r="T8" s="11">
-        <v>65.4967378430907</v>
+        <v>65.67317529128781</v>
       </c>
       <c r="U8" s="11">
-        <v>56.1196811919735</v>
+        <v>56.6728841413645</v>
       </c>
       <c r="V8" s="11">
-        <v>92.15909443292691</v>
+        <v>91.9131800315977</v>
       </c>
       <c r="W8" s="11">
-        <v>43.0905593898346</v>
+        <v>43.489020634561</v>
       </c>
       <c r="X8" s="11">
         <v>70.6176163576279</v>
       </c>
       <c r="Y8" s="11">
-        <v>84.5954869688205</v>
+        <v>85.5542096222573</v>
       </c>
       <c r="Z8" s="11">
-        <v>90.2970393239019</v>
+        <v>91.5223592381755</v>
       </c>
       <c r="AA8" s="11">
-        <v>78.89393461373911</v>
+        <v>79.5860600063392</v>
       </c>
       <c r="AB8" s="11">
-        <v>65.2504761643474</v>
+        <v>65.41584802372491</v>
       </c>
       <c r="AC8" s="11">
-        <v>56.4925812035216</v>
+        <v>56.4869807629629</v>
       </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
@@ -2368,82 +2370,82 @@
         <v>43</v>
       </c>
       <c r="D9" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E9" s="11">
-        <v>49.119540667756</v>
+        <v>49.1857638617058</v>
       </c>
       <c r="F9" s="11">
-        <v>52.6698255819544</v>
+        <v>51.7356954607941</v>
       </c>
       <c r="G9" s="11">
-        <v>45.5692557535575</v>
+        <v>46.6358322626174</v>
       </c>
       <c r="H9" s="11">
-        <v>45.1142538437403</v>
+        <v>40.9384331593514</v>
       </c>
       <c r="I9" s="11">
-        <v>69.0308537704578</v>
+        <v>53.9746295816379</v>
       </c>
       <c r="J9" s="11">
-        <v>48.0211881246975</v>
+        <v>45.5606477063712</v>
       </c>
       <c r="K9" s="11">
-        <v>56.5482130310128</v>
+        <v>57.3616949006035</v>
       </c>
       <c r="L9" s="11">
         <v>6.85676044879287</v>
       </c>
       <c r="M9" s="11">
-        <v>39.7453440462242</v>
+        <v>39.5351055645191</v>
       </c>
       <c r="N9" s="11">
-        <v>39.3317617771878</v>
+        <v>36.7240100322192</v>
       </c>
       <c r="O9" s="11">
-        <v>40.1589263152606</v>
+        <v>42.346201096819</v>
       </c>
       <c r="P9" s="11">
-        <v>44.6597128525735</v>
+        <v>43.2197675285254</v>
       </c>
       <c r="Q9" s="11">
-        <v>37.3393443480762</v>
+        <v>36.1309062571268</v>
       </c>
       <c r="R9" s="11">
-        <v>15.435752263624</v>
+        <v>14.3961931370277</v>
       </c>
       <c r="S9" s="11">
-        <v>59.2429364325284</v>
+        <v>57.8656193772258</v>
       </c>
       <c r="T9" s="11">
-        <v>44.100382644194</v>
+        <v>44.7301913626238</v>
       </c>
       <c r="U9" s="11">
-        <v>58.180360763272</v>
+        <v>60.5815433749819</v>
       </c>
       <c r="V9" s="11">
-        <v>53.9086837823587</v>
+        <v>54.2086663888686</v>
       </c>
       <c r="W9" s="11">
-        <v>44.734681498593</v>
+        <v>44.5527511540925</v>
       </c>
       <c r="X9" s="11">
         <v>19.5778045325524</v>
       </c>
       <c r="Y9" s="11">
-        <v>57.0533237794685</v>
+        <v>52.3654375473809</v>
       </c>
       <c r="Z9" s="11">
-        <v>57.6838384456155</v>
+        <v>54.2810419991647</v>
       </c>
       <c r="AA9" s="11">
-        <v>56.4228091133215</v>
+        <v>50.4498330955971</v>
       </c>
       <c r="AB9" s="11">
-        <v>46.1643502572462</v>
+        <v>44.4088450557105</v>
       </c>
       <c r="AC9" s="11">
-        <v>45.4120315549099</v>
+        <v>43.814306292118</v>
       </c>
     </row>
     <row r="10" ht="20.05" customHeight="1">
@@ -2457,82 +2459,82 @@
         <v>45</v>
       </c>
       <c r="D10" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E10" s="11">
-        <v>61.6244066506475</v>
+        <v>63.6148204124102</v>
       </c>
       <c r="F10" s="11">
-        <v>54.4234748534743</v>
+        <v>52.131599698993</v>
       </c>
       <c r="G10" s="11">
-        <v>68.8253384478206</v>
+        <v>75.09804112582729</v>
       </c>
       <c r="H10" s="11">
-        <v>55.6599274107975</v>
+        <v>54.4534431631118</v>
       </c>
       <c r="I10" s="11">
-        <v>99.8203586960483</v>
+        <v>99.9029009714297</v>
       </c>
       <c r="J10" s="11">
-        <v>44.9878803140104</v>
+        <v>43.4175091889768</v>
       </c>
       <c r="K10" s="11">
-        <v>47.919226184268</v>
+        <v>44.5811180431772</v>
       </c>
       <c r="L10" s="11">
         <v>29.9122444488634</v>
       </c>
       <c r="M10" s="11">
-        <v>37.4998804353549</v>
+        <v>40.2860403452132</v>
       </c>
       <c r="N10" s="11">
-        <v>36.407736791652</v>
+        <v>35.2194661779455</v>
       </c>
       <c r="O10" s="11">
-        <v>38.5920240790579</v>
+        <v>45.352614512481</v>
       </c>
       <c r="P10" s="11">
-        <v>51.5947381656</v>
+        <v>52.7847679735784</v>
       </c>
       <c r="Q10" s="11">
-        <v>24.3226611598584</v>
+        <v>17.1400622711886</v>
       </c>
       <c r="R10" s="11">
-        <v>1.70386390608634</v>
+        <v>0.998640646402645</v>
       </c>
       <c r="S10" s="11">
-        <v>46.9414584136304</v>
+        <v>33.2814838959745</v>
       </c>
       <c r="T10" s="11">
-        <v>60.5801328887712</v>
+        <v>60.0991695619931</v>
       </c>
       <c r="U10" s="11">
-        <v>99.99998153417251</v>
+        <v>99.99997307345041</v>
       </c>
       <c r="V10" s="11">
-        <v>68.2544070974174</v>
+        <v>69.0986366755327</v>
       </c>
       <c r="W10" s="11">
-        <v>54.8288267385729</v>
+        <v>52.0607523140672</v>
       </c>
       <c r="X10" s="11">
         <v>19.2373161849219</v>
       </c>
       <c r="Y10" s="11">
-        <v>58.4507294689124</v>
+        <v>60.1490437868778</v>
       </c>
       <c r="Z10" s="11">
-        <v>59.7238728156385</v>
+        <v>66.6004694235005</v>
       </c>
       <c r="AA10" s="11">
-        <v>57.1775861221863</v>
+        <v>53.697618150255</v>
       </c>
       <c r="AB10" s="11">
-        <v>47.7845078391807</v>
+        <v>45.7960918733531</v>
       </c>
       <c r="AC10" s="11">
-        <v>49.6896230023903</v>
+        <v>49.2904299234658</v>
       </c>
     </row>
     <row r="11" ht="20.05" customHeight="1">
@@ -2546,82 +2548,82 @@
         <v>47</v>
       </c>
       <c r="D11" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E11" s="11">
-        <v>43.2881749036793</v>
+        <v>41.0669041579741</v>
       </c>
       <c r="F11" s="11">
-        <v>50.9795050740683</v>
+        <v>50.9052436508224</v>
       </c>
       <c r="G11" s="11">
-        <v>35.5968447332903</v>
+        <v>31.2285646651259</v>
       </c>
       <c r="H11" s="11">
-        <v>57.4903130712334</v>
+        <v>59.7863177728153</v>
       </c>
       <c r="I11" s="11">
-        <v>48.1386508843927</v>
+        <v>58.5337557490196</v>
       </c>
       <c r="J11" s="11">
-        <v>44.8857099714339</v>
+        <v>43.3522521904935</v>
       </c>
       <c r="K11" s="11">
-        <v>44.0089181010581</v>
+        <v>44.3312898236993</v>
       </c>
       <c r="L11" s="11">
         <v>92.92797332804911</v>
       </c>
       <c r="M11" s="11">
-        <v>55.3698522167446</v>
+        <v>49.0006081118266</v>
       </c>
       <c r="N11" s="11">
-        <v>69.2220237794788</v>
+        <v>65.278959957444</v>
       </c>
       <c r="O11" s="11">
-        <v>41.5176806540103</v>
+        <v>32.7222562662092</v>
       </c>
       <c r="P11" s="11">
-        <v>52.0494467305525</v>
+        <v>49.951276680872</v>
       </c>
       <c r="Q11" s="11">
-        <v>72.48574741115689</v>
+        <v>75.1296296581945</v>
       </c>
       <c r="R11" s="11">
-        <v>76.64537249326069</v>
+        <v>79.5980138368426</v>
       </c>
       <c r="S11" s="11">
-        <v>68.32612232905301</v>
+        <v>70.6612454795463</v>
       </c>
       <c r="T11" s="11">
-        <v>71.8983968146739</v>
+        <v>68.1160507805143</v>
       </c>
       <c r="U11" s="11">
-        <v>44.7144923114232</v>
+        <v>41.8803607101925</v>
       </c>
       <c r="V11" s="11">
-        <v>73.53530340761969</v>
+        <v>67.3796447361954</v>
       </c>
       <c r="W11" s="11">
-        <v>78.829095527696</v>
+        <v>72.6895016637127</v>
       </c>
       <c r="X11" s="11">
         <v>90.5146960119566</v>
       </c>
       <c r="Y11" s="11">
-        <v>57.7448337111512</v>
+        <v>59.3155157941368</v>
       </c>
       <c r="Z11" s="11">
-        <v>54.4547544589536</v>
+        <v>60.4912673075758</v>
       </c>
       <c r="AA11" s="11">
-        <v>61.0349129633489</v>
+        <v>58.1397642806977</v>
       </c>
       <c r="AB11" s="11">
-        <v>67.376325978994</v>
+        <v>67.52039874428191</v>
       </c>
       <c r="AC11" s="11">
-        <v>59.7128863547732</v>
+        <v>58.7358377125769</v>
       </c>
     </row>
     <row r="12" ht="20.05" customHeight="1">
@@ -2635,82 +2637,82 @@
         <v>49</v>
       </c>
       <c r="D12" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E12" s="11">
-        <v>53.2109556992515</v>
+        <v>53.1524200399084</v>
       </c>
       <c r="F12" s="11">
-        <v>47.5736809894682</v>
+        <v>46.7527616053528</v>
       </c>
       <c r="G12" s="11">
-        <v>58.8482304090349</v>
+        <v>59.5520784744639</v>
       </c>
       <c r="H12" s="11">
-        <v>57.8420090898048</v>
+        <v>58.4627276527144</v>
       </c>
       <c r="I12" s="11">
-        <v>45.7087390920427</v>
+        <v>46.0889516023144</v>
       </c>
       <c r="J12" s="11">
-        <v>60.6495810904109</v>
+        <v>61.9258154913497</v>
       </c>
       <c r="K12" s="11">
-        <v>46.4505051065469</v>
+        <v>47.276932446975</v>
       </c>
       <c r="L12" s="11">
         <v>78.55921107021859</v>
       </c>
       <c r="M12" s="11">
-        <v>36.6574751769696</v>
+        <v>35.3403962041987</v>
       </c>
       <c r="N12" s="11">
-        <v>23.9051939132259</v>
+        <v>21.2736436923487</v>
       </c>
       <c r="O12" s="11">
-        <v>49.4097564407133</v>
+        <v>49.4071487160486</v>
       </c>
       <c r="P12" s="11">
-        <v>49.2368133220086</v>
+        <v>48.9851812989405</v>
       </c>
       <c r="Q12" s="11">
-        <v>56.5395215738936</v>
+        <v>56.5487747510382</v>
       </c>
       <c r="R12" s="11">
-        <v>72.3016698205634</v>
+        <v>72.6729592642567</v>
       </c>
       <c r="S12" s="11">
-        <v>40.7773733272238</v>
+        <v>40.4245902378197</v>
       </c>
       <c r="T12" s="11">
-        <v>51.2420009961826</v>
+        <v>51.6849426188235</v>
       </c>
       <c r="U12" s="11">
-        <v>41.8334658834237</v>
+        <v>43.3571525791585</v>
       </c>
       <c r="V12" s="11">
-        <v>58.0734038633065</v>
+        <v>57.9664404669471</v>
       </c>
       <c r="W12" s="11">
-        <v>26.2949123625962</v>
+        <v>26.6499555537841</v>
       </c>
       <c r="X12" s="11">
         <v>78.7662218754041</v>
       </c>
       <c r="Y12" s="11">
-        <v>48.1308400071359</v>
+        <v>48.7129760718925</v>
       </c>
       <c r="Z12" s="11">
-        <v>41.9172859551308</v>
+        <v>42.6960298085032</v>
       </c>
       <c r="AA12" s="11">
-        <v>54.344394059141</v>
+        <v>54.7299223352819</v>
       </c>
       <c r="AB12" s="11">
-        <v>51.9707875257374</v>
+        <v>52.3155644805847</v>
       </c>
       <c r="AC12" s="11">
-        <v>50.603800423873</v>
+        <v>50.6503728897626</v>
       </c>
     </row>
     <row r="13" ht="20.05" customHeight="1">
@@ -2724,82 +2726,82 @@
         <v>51</v>
       </c>
       <c r="D13" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E13" s="11">
-        <v>52.407849034099</v>
+        <v>53.3458598026559</v>
       </c>
       <c r="F13" s="11">
-        <v>51.7924086553617</v>
+        <v>52.0550857939305</v>
       </c>
       <c r="G13" s="11">
-        <v>53.0232894128364</v>
+        <v>54.6366338113814</v>
       </c>
       <c r="H13" s="11">
-        <v>59.2252076785413</v>
+        <v>59.0920134245811</v>
       </c>
       <c r="I13" s="11">
-        <v>60.1157612524537</v>
+        <v>58.4296186364183</v>
       </c>
       <c r="J13" s="11">
-        <v>50.5754325816834</v>
+        <v>52.5475929232586</v>
       </c>
       <c r="K13" s="11">
-        <v>49.6678046914852</v>
+        <v>48.8490099501046</v>
       </c>
       <c r="L13" s="11">
         <v>76.5418321885429</v>
       </c>
       <c r="M13" s="11">
-        <v>49.7186818743449</v>
+        <v>47.1355130933915</v>
       </c>
       <c r="N13" s="11">
-        <v>51.0000107335339</v>
+        <v>48.9256029469218</v>
       </c>
       <c r="O13" s="11">
-        <v>48.4373530151559</v>
+        <v>45.3454232398613</v>
       </c>
       <c r="P13" s="11">
-        <v>53.7839128623284</v>
+        <v>53.1911287735428</v>
       </c>
       <c r="Q13" s="11">
-        <v>62.4845955658316</v>
+        <v>61.4473301495084</v>
       </c>
       <c r="R13" s="11">
-        <v>83.58774702723009</v>
+        <v>81.9350549502831</v>
       </c>
       <c r="S13" s="11">
-        <v>41.3814441044332</v>
+        <v>40.9596053487338</v>
       </c>
       <c r="T13" s="11">
-        <v>43.5584209044082</v>
+        <v>44.1499434062878</v>
       </c>
       <c r="U13" s="11">
-        <v>37.5628791657285</v>
+        <v>37.3352433767415</v>
       </c>
       <c r="V13" s="11">
-        <v>36.0083030829808</v>
+        <v>37.7460337271683</v>
       </c>
       <c r="W13" s="11">
-        <v>28.4765728087296</v>
+        <v>29.3325679610474</v>
       </c>
       <c r="X13" s="11">
         <v>72.1859285601942</v>
       </c>
       <c r="Y13" s="11">
-        <v>44.7090861630516</v>
+        <v>45.5276068421875</v>
       </c>
       <c r="Z13" s="11">
-        <v>32.0388980617003</v>
+        <v>34.2575080565553</v>
       </c>
       <c r="AA13" s="11">
-        <v>57.3792742644029</v>
+        <v>56.7977056278197</v>
       </c>
       <c r="AB13" s="11">
-        <v>50.2507008777638</v>
+        <v>50.3749601326613</v>
       </c>
       <c r="AC13" s="11">
-        <v>52.0173068700461</v>
+        <v>51.783044453102</v>
       </c>
     </row>
     <row r="14" ht="20.05" customHeight="1">
@@ -2813,82 +2815,82 @@
         <v>53</v>
       </c>
       <c r="D14" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E14" s="11">
-        <v>47.5582240059444</v>
+        <v>47.0718942373761</v>
       </c>
       <c r="F14" s="11">
-        <v>68.94625946272249</v>
+        <v>67.9266745832022</v>
       </c>
       <c r="G14" s="11">
-        <v>26.1701885491664</v>
+        <v>26.2171138915499</v>
       </c>
       <c r="H14" s="11">
-        <v>57.7387199870173</v>
+        <v>56.0695946362325</v>
       </c>
       <c r="I14" s="11">
-        <v>78.12813455061671</v>
+        <v>69.03295879089519</v>
       </c>
       <c r="J14" s="11">
-        <v>56.1514825622664</v>
+        <v>56.019798264087</v>
       </c>
       <c r="K14" s="11">
-        <v>61.4784345793868</v>
+        <v>64.02879323414891</v>
       </c>
       <c r="L14" s="11">
         <v>35.196828255799</v>
       </c>
       <c r="M14" s="11">
-        <v>32.5391222554982</v>
+        <v>28.8243858640797</v>
       </c>
       <c r="N14" s="11">
-        <v>7.81911674276298</v>
+        <v>6.88408457485569</v>
       </c>
       <c r="O14" s="11">
-        <v>57.2591277682335</v>
+        <v>50.7646871533037</v>
       </c>
       <c r="P14" s="11">
-        <v>45.9453554161533</v>
+        <v>43.9886249125628</v>
       </c>
       <c r="Q14" s="11">
-        <v>57.9474396801787</v>
+        <v>58.6918494453111</v>
       </c>
       <c r="R14" s="11">
-        <v>33.1528361286407</v>
+        <v>33.5864316445458</v>
       </c>
       <c r="S14" s="11">
-        <v>82.74204323171659</v>
+        <v>83.7972672460764</v>
       </c>
       <c r="T14" s="11">
-        <v>66.7215614776312</v>
+        <v>66.782063365517</v>
       </c>
       <c r="U14" s="11">
-        <v>78.12956737851999</v>
+        <v>77.5569097216665</v>
       </c>
       <c r="V14" s="11">
-        <v>77.4536496719146</v>
+        <v>79.7444974100916</v>
       </c>
       <c r="W14" s="11">
-        <v>63.7452636933348</v>
+        <v>62.2690811635545</v>
       </c>
       <c r="X14" s="11">
         <v>47.5577651667555</v>
       </c>
       <c r="Y14" s="11">
-        <v>67.7690208769759</v>
+        <v>66.4526067233687</v>
       </c>
       <c r="Z14" s="11">
-        <v>51.6339091333034</v>
+        <v>50.3876696476648</v>
       </c>
       <c r="AA14" s="11">
-        <v>83.9041326206485</v>
+        <v>82.5175437990725</v>
       </c>
       <c r="AB14" s="11">
-        <v>64.14600734492861</v>
+        <v>63.9755065113989</v>
       </c>
       <c r="AC14" s="11">
-        <v>55.0456813805409</v>
+        <v>53.9820657119809</v>
       </c>
     </row>
     <row r="15" ht="20.05" customHeight="1">
@@ -2902,82 +2904,82 @@
         <v>55</v>
       </c>
       <c r="D15" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E15" s="11">
-        <v>40.4077106123623</v>
+        <v>39.2279774911739</v>
       </c>
       <c r="F15" s="11">
-        <v>22.449517774596</v>
+        <v>19.120543711559</v>
       </c>
       <c r="G15" s="11">
-        <v>58.3659034501286</v>
+        <v>59.3354112707887</v>
       </c>
       <c r="H15" s="11">
-        <v>32.8704354219929</v>
+        <v>31.9921467562336</v>
       </c>
       <c r="I15" s="11">
-        <v>30.5907532275492</v>
+        <v>26.641398688416</v>
       </c>
       <c r="J15" s="11">
-        <v>39.4257278324151</v>
+        <v>38.6879046840132</v>
       </c>
       <c r="K15" s="11">
-        <v>52.115086185142</v>
+        <v>53.2891092096399</v>
       </c>
       <c r="L15" s="11">
         <v>9.35017444286518</v>
       </c>
       <c r="M15" s="11">
-        <v>47.3259144381642</v>
+        <v>50.7718750139878</v>
       </c>
       <c r="N15" s="11">
-        <v>49.4061434258156</v>
+        <v>53.6312488496597</v>
       </c>
       <c r="O15" s="11">
-        <v>45.2456854505128</v>
+        <v>47.9125011783159</v>
       </c>
       <c r="P15" s="11">
-        <v>40.2013534908398</v>
+        <v>40.6639997537984</v>
       </c>
       <c r="Q15" s="11">
-        <v>36.6761547578788</v>
+        <v>38.6138210281167</v>
       </c>
       <c r="R15" s="11">
-        <v>27.7894838159433</v>
+        <v>32.1575718353606</v>
       </c>
       <c r="S15" s="11">
-        <v>45.5628256998143</v>
+        <v>45.0700702208729</v>
       </c>
       <c r="T15" s="11">
-        <v>43.782148826352</v>
+        <v>43.1617698506267</v>
       </c>
       <c r="U15" s="11">
-        <v>35.2189649354809</v>
+        <v>34.2533051681783</v>
       </c>
       <c r="V15" s="11">
-        <v>53.4926039216843</v>
+        <v>52.3090905679656</v>
       </c>
       <c r="W15" s="11">
-        <v>72.7427402314561</v>
+        <v>72.41039744957619</v>
       </c>
       <c r="X15" s="11">
         <v>13.6742862167869</v>
       </c>
       <c r="Y15" s="11">
-        <v>62.4897373991251</v>
+        <v>64.9601508956446</v>
       </c>
       <c r="Z15" s="11">
-        <v>82.86995236503751</v>
+        <v>84.1575069969432</v>
       </c>
       <c r="AA15" s="11">
-        <v>42.1095224332126</v>
+        <v>45.762794794346</v>
       </c>
       <c r="AB15" s="11">
-        <v>47.649346994452</v>
+        <v>48.911913924796</v>
       </c>
       <c r="AC15" s="11">
-        <v>43.9253502426459</v>
+        <v>44.7879568392972</v>
       </c>
     </row>
     <row r="16" ht="20.05" customHeight="1">
@@ -2991,82 +2993,82 @@
         <v>57</v>
       </c>
       <c r="D16" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E16" s="11">
-        <v>48.0620483591238</v>
+        <v>49.6049706837891</v>
       </c>
       <c r="F16" s="11">
-        <v>44.7045309123271</v>
+        <v>45.3979465455487</v>
       </c>
       <c r="G16" s="11">
-        <v>51.4195658059206</v>
+        <v>53.8119948220295</v>
       </c>
       <c r="H16" s="11">
-        <v>56.8586619939322</v>
+        <v>56.5791740055733</v>
       </c>
       <c r="I16" s="11">
-        <v>54.8711141772469</v>
+        <v>54.2509193070073</v>
       </c>
       <c r="J16" s="11">
-        <v>48.051849460144</v>
+        <v>48.7984495297023</v>
       </c>
       <c r="K16" s="11">
-        <v>50.9251628607177</v>
+        <v>49.6808057079637</v>
       </c>
       <c r="L16" s="11">
         <v>73.5865214776201</v>
       </c>
       <c r="M16" s="11">
-        <v>47.3007708021951</v>
+        <v>49.012717506296</v>
       </c>
       <c r="N16" s="11">
-        <v>54.8134011771517</v>
+        <v>55.2684391751522</v>
       </c>
       <c r="O16" s="11">
-        <v>39.7881404272385</v>
+        <v>42.7569958374398</v>
       </c>
       <c r="P16" s="11">
-        <v>50.740493718417</v>
+        <v>51.7322873985528</v>
       </c>
       <c r="Q16" s="11">
-        <v>63.1349628849896</v>
+        <v>60.9099254935959</v>
       </c>
       <c r="R16" s="11">
-        <v>76.32095979742461</v>
+        <v>74.0886609960299</v>
       </c>
       <c r="S16" s="11">
-        <v>49.9489659725546</v>
+        <v>47.7311899911618</v>
       </c>
       <c r="T16" s="11">
-        <v>57.0808995998376</v>
+        <v>56.7342842290175</v>
       </c>
       <c r="U16" s="11">
-        <v>31.9986147752162</v>
+        <v>33.3853540255774</v>
       </c>
       <c r="V16" s="11">
-        <v>63.3968001166323</v>
+        <v>60.8994131703113</v>
       </c>
       <c r="W16" s="11">
-        <v>54.7042520879745</v>
+        <v>54.4284383006537</v>
       </c>
       <c r="X16" s="11">
         <v>78.2239314195275</v>
       </c>
       <c r="Y16" s="11">
-        <v>64.056850575360</v>
+        <v>66.9775107228655</v>
       </c>
       <c r="Z16" s="11">
-        <v>79.2035165585439</v>
+        <v>81.49757383621009</v>
       </c>
       <c r="AA16" s="11">
-        <v>48.910184592176</v>
+        <v>52.4574476095208</v>
       </c>
       <c r="AB16" s="11">
-        <v>61.4242376867291</v>
+        <v>61.5405734818263</v>
       </c>
       <c r="AC16" s="11">
-        <v>56.0823657025731</v>
+        <v>56.6364304401895</v>
       </c>
     </row>
     <row r="17" ht="20.05" customHeight="1">
@@ -3080,82 +3082,82 @@
         <v>59</v>
       </c>
       <c r="D17" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E17" s="11">
-        <v>45.4052457176358</v>
+        <v>46.2235079500868</v>
       </c>
       <c r="F17" s="11">
-        <v>36.9736554734908</v>
+        <v>38.1139552306872</v>
       </c>
       <c r="G17" s="11">
-        <v>53.8368359617807</v>
+        <v>54.3330606694864</v>
       </c>
       <c r="H17" s="11">
-        <v>42.2481087247028</v>
+        <v>43.3516780814797</v>
       </c>
       <c r="I17" s="11">
-        <v>61.177649283878</v>
+        <v>64.06123444071839</v>
       </c>
       <c r="J17" s="11">
-        <v>35.3464688037319</v>
+        <v>35.5309213012908</v>
       </c>
       <c r="K17" s="11">
-        <v>49.7324643247131</v>
+        <v>51.0787040974215</v>
       </c>
       <c r="L17" s="11">
         <v>22.7358524864882</v>
       </c>
       <c r="M17" s="11">
-        <v>38.5631188943882</v>
+        <v>37.9917310266105</v>
       </c>
       <c r="N17" s="11">
-        <v>31.0858317505147</v>
+        <v>29.4958750015519</v>
       </c>
       <c r="O17" s="11">
-        <v>46.0404060382617</v>
+        <v>46.487587051669</v>
       </c>
       <c r="P17" s="11">
-        <v>42.0721577789089</v>
+        <v>42.522305686059</v>
       </c>
       <c r="Q17" s="11">
-        <v>49.8378985287464</v>
+        <v>47.5862806631625</v>
       </c>
       <c r="R17" s="11">
-        <v>53.299342561720</v>
+        <v>49.5873581478659</v>
       </c>
       <c r="S17" s="11">
-        <v>46.3764544957728</v>
+        <v>45.5852031784591</v>
       </c>
       <c r="T17" s="11">
-        <v>51.3910669332235</v>
+        <v>51.6056825767286</v>
       </c>
       <c r="U17" s="11">
-        <v>74.8094245314274</v>
+        <v>74.19810780342441</v>
       </c>
       <c r="V17" s="11">
-        <v>50.3940627965391</v>
+        <v>51.7221365501916</v>
       </c>
       <c r="W17" s="11">
-        <v>39.9415901853915</v>
+        <v>40.0832957337623</v>
       </c>
       <c r="X17" s="11">
         <v>40.4191902195358</v>
       </c>
       <c r="Y17" s="11">
-        <v>54.8902900300118</v>
+        <v>56.1555266469274</v>
       </c>
       <c r="Z17" s="11">
-        <v>54.8571150848504</v>
+        <v>55.6685619935723</v>
       </c>
       <c r="AA17" s="11">
-        <v>54.9234649751732</v>
+        <v>56.6424913002824</v>
       </c>
       <c r="AB17" s="11">
-        <v>52.0397518306606</v>
+        <v>51.7824966289395</v>
       </c>
       <c r="AC17" s="11">
-        <v>47.0559548047848</v>
+        <v>47.1524011574992</v>
       </c>
     </row>
     <row r="18" ht="20.05" customHeight="1">
@@ -3169,82 +3171,82 @@
         <v>61</v>
       </c>
       <c r="D18" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E18" s="11">
-        <v>43.9846832335828</v>
+        <v>45.4387526253711</v>
       </c>
       <c r="F18" s="11">
-        <v>33.5126929660996</v>
+        <v>34.3503646167479</v>
       </c>
       <c r="G18" s="11">
-        <v>54.4566735010661</v>
+        <v>56.5271406339942</v>
       </c>
       <c r="H18" s="11">
-        <v>51.6407099670925</v>
+        <v>50.542616895398</v>
       </c>
       <c r="I18" s="11">
-        <v>45.1051679860389</v>
+        <v>44.0705555686575</v>
       </c>
       <c r="J18" s="11">
-        <v>56.1090796117259</v>
+        <v>52.6339011572739</v>
       </c>
       <c r="K18" s="11">
-        <v>55.9511277917648</v>
+        <v>56.0685463768202</v>
       </c>
       <c r="L18" s="11">
         <v>49.3974644788403</v>
       </c>
       <c r="M18" s="11">
-        <v>62.7252488262574</v>
+        <v>63.8951387596123</v>
       </c>
       <c r="N18" s="11">
-        <v>65.91661502804889</v>
+        <v>67.1302461085065</v>
       </c>
       <c r="O18" s="11">
-        <v>59.5338826244658</v>
+        <v>60.6600314107181</v>
       </c>
       <c r="P18" s="11">
-        <v>52.7835473423109</v>
+        <v>53.2921694267938</v>
       </c>
       <c r="Q18" s="11">
-        <v>51.914871133982</v>
+        <v>52.4801650034449</v>
       </c>
       <c r="R18" s="11">
-        <v>63.6846274469383</v>
+        <v>66.8980734252137</v>
       </c>
       <c r="S18" s="11">
-        <v>40.1451148210256</v>
+        <v>38.0622565816761</v>
       </c>
       <c r="T18" s="11">
-        <v>38.2540533902093</v>
+        <v>37.4732826555831</v>
       </c>
       <c r="U18" s="11">
-        <v>28.5023180588798</v>
+        <v>27.7702242368258</v>
       </c>
       <c r="V18" s="11">
-        <v>26.4734089640285</v>
+        <v>27.0019325317847</v>
       </c>
       <c r="W18" s="11">
-        <v>56.9292000475575</v>
+        <v>54.0096873633502</v>
       </c>
       <c r="X18" s="11">
         <v>41.1112864903715</v>
       </c>
       <c r="Y18" s="11">
-        <v>45.8914965114522</v>
+        <v>46.5066894319199</v>
       </c>
       <c r="Z18" s="11">
-        <v>46.3308517930953</v>
+        <v>45.8582054950386</v>
       </c>
       <c r="AA18" s="11">
-        <v>45.4521412298091</v>
+        <v>47.1551733688012</v>
       </c>
       <c r="AB18" s="11">
-        <v>45.3534736785478</v>
+        <v>45.4867123636493</v>
       </c>
       <c r="AC18" s="11">
-        <v>49.0685105104294</v>
+        <v>49.3894408952215</v>
       </c>
     </row>
     <row r="19" ht="20.05" customHeight="1">
@@ -3258,82 +3260,82 @@
         <v>63</v>
       </c>
       <c r="D19" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E19" s="11">
-        <v>60.4109997600605</v>
+        <v>60.2126409759776</v>
       </c>
       <c r="F19" s="11">
-        <v>34.4484035969771</v>
+        <v>33.037335954250</v>
       </c>
       <c r="G19" s="11">
-        <v>86.3735959231439</v>
+        <v>87.3879459977052</v>
       </c>
       <c r="H19" s="11">
-        <v>38.7313582130292</v>
+        <v>37.2150499262398</v>
       </c>
       <c r="I19" s="11">
-        <v>33.9518061916586</v>
+        <v>27.5083098352914</v>
       </c>
       <c r="J19" s="11">
-        <v>28.8913057379291</v>
+        <v>29.0790557151455</v>
       </c>
       <c r="K19" s="11">
-        <v>63.0994032996966</v>
+        <v>63.2899165316898</v>
       </c>
       <c r="L19" s="11">
         <v>28.9829176228326</v>
       </c>
       <c r="M19" s="11">
-        <v>59.5036913231176</v>
+        <v>58.0372542672407</v>
       </c>
       <c r="N19" s="11">
-        <v>62.8213737855277</v>
+        <v>60.7043893615838</v>
       </c>
       <c r="O19" s="11">
-        <v>56.1860088607075</v>
+        <v>55.3701191728975</v>
       </c>
       <c r="P19" s="11">
-        <v>52.8820164320691</v>
+        <v>51.8216483898194</v>
       </c>
       <c r="Q19" s="11">
-        <v>22.3252284250477</v>
+        <v>22.3560673211951</v>
       </c>
       <c r="R19" s="11">
-        <v>28.6200811787088</v>
+        <v>30.2927764935704</v>
       </c>
       <c r="S19" s="11">
-        <v>16.0303756713865</v>
+        <v>14.4193581488199</v>
       </c>
       <c r="T19" s="11">
-        <v>45.7021394104062</v>
+        <v>44.6974790248642</v>
       </c>
       <c r="U19" s="11">
-        <v>36.0179512838566</v>
+        <v>35.1027365997153</v>
       </c>
       <c r="V19" s="11">
-        <v>65.6417748106483</v>
+        <v>63.6199234280758</v>
       </c>
       <c r="W19" s="11">
-        <v>46.4295421252381</v>
+        <v>45.3479666497842</v>
       </c>
       <c r="X19" s="11">
         <v>34.7192894218817</v>
       </c>
       <c r="Y19" s="11">
-        <v>63.721581449831</v>
+        <v>62.4808904492057</v>
       </c>
       <c r="Z19" s="11">
-        <v>81.7360085033086</v>
+        <v>79.25311203935939</v>
       </c>
       <c r="AA19" s="11">
-        <v>45.7071543963534</v>
+        <v>45.708668859052</v>
       </c>
       <c r="AB19" s="11">
-        <v>43.9163164284283</v>
+        <v>43.1781455984217</v>
       </c>
       <c r="AC19" s="11">
-        <v>48.3991664302487</v>
+        <v>47.4998969941205</v>
       </c>
     </row>
     <row r="20" ht="20.05" customHeight="1">
@@ -3347,82 +3349,82 @@
         <v>65</v>
       </c>
       <c r="D20" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E20" s="11">
-        <v>49.2017792425554</v>
+        <v>47.9805582285337</v>
       </c>
       <c r="F20" s="11">
-        <v>48.6648963885863</v>
+        <v>49.5859636969077</v>
       </c>
       <c r="G20" s="11">
-        <v>49.7386620965245</v>
+        <v>46.3751527601597</v>
       </c>
       <c r="H20" s="11">
-        <v>46.2487118081879</v>
+        <v>44.0587530845594</v>
       </c>
       <c r="I20" s="11">
-        <v>33.7195811217244</v>
+        <v>31.3332830616243</v>
       </c>
       <c r="J20" s="11">
-        <v>70.3275513754475</v>
+        <v>68.9945498028375</v>
       </c>
       <c r="K20" s="11">
-        <v>39.3591977232428</v>
+        <v>34.3186624614388</v>
       </c>
       <c r="L20" s="11">
         <v>41.5885170123369</v>
       </c>
       <c r="M20" s="11">
-        <v>68.4453412052177</v>
+        <v>68.35788217391919</v>
       </c>
       <c r="N20" s="11">
-        <v>59.6428358719475</v>
+        <v>58.2094934430783</v>
       </c>
       <c r="O20" s="11">
-        <v>77.24784653848801</v>
+        <v>78.5062709047601</v>
       </c>
       <c r="P20" s="11">
-        <v>54.6319440853204</v>
+        <v>53.4657311623374</v>
       </c>
       <c r="Q20" s="11">
-        <v>59.6235540832703</v>
+        <v>61.1506389639</v>
       </c>
       <c r="R20" s="11">
-        <v>79.1177851059517</v>
+        <v>80.39547171526669</v>
       </c>
       <c r="S20" s="11">
-        <v>40.1293230605889</v>
+        <v>41.9058062125332</v>
       </c>
       <c r="T20" s="11">
-        <v>36.1009266144685</v>
+        <v>36.1800646812429</v>
       </c>
       <c r="U20" s="11">
-        <v>28.3111689872134</v>
+        <v>28.9533198325838</v>
       </c>
       <c r="V20" s="11">
-        <v>9.244535700072539</v>
+        <v>10.4239500448885</v>
       </c>
       <c r="W20" s="11">
-        <v>69.2533067380496</v>
+        <v>67.7482938149607</v>
       </c>
       <c r="X20" s="11">
         <v>37.5946950325384</v>
       </c>
       <c r="Y20" s="11">
-        <v>18.586450642446</v>
+        <v>18.825364449410</v>
       </c>
       <c r="Z20" s="11">
-        <v>13.0533773711657</v>
+        <v>13.0823663096163</v>
       </c>
       <c r="AA20" s="11">
-        <v>24.1195239137263</v>
+        <v>24.5683625892037</v>
       </c>
       <c r="AB20" s="11">
-        <v>38.1036437800616</v>
+        <v>38.7186893648509</v>
       </c>
       <c r="AC20" s="11">
-        <v>46.367793932691</v>
+        <v>46.0922102635942</v>
       </c>
     </row>
     <row r="21" ht="20.05" customHeight="1">
@@ -3436,82 +3438,82 @@
         <v>67</v>
       </c>
       <c r="D21" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E21" s="11">
-        <v>44.8837940090152</v>
+        <v>44.5298581739801</v>
       </c>
       <c r="F21" s="11">
-        <v>53.6099939121079</v>
+        <v>54.5542915112398</v>
       </c>
       <c r="G21" s="11">
-        <v>36.1575941059225</v>
+        <v>34.5054248367204</v>
       </c>
       <c r="H21" s="11">
-        <v>55.0730696395621</v>
+        <v>53.669188182959</v>
       </c>
       <c r="I21" s="11">
-        <v>36.0991383320229</v>
+        <v>30.0737995752545</v>
       </c>
       <c r="J21" s="11">
-        <v>82.3334358862504</v>
+        <v>82.98301893888519</v>
       </c>
       <c r="K21" s="11">
-        <v>43.4059875067574</v>
+        <v>43.1662173844785</v>
       </c>
       <c r="L21" s="11">
         <v>58.4537168332179</v>
       </c>
       <c r="M21" s="11">
-        <v>65.0179159463959</v>
+        <v>65.26020054393049</v>
       </c>
       <c r="N21" s="11">
-        <v>67.3355419949704</v>
+        <v>64.989581627017</v>
       </c>
       <c r="O21" s="11">
-        <v>62.7002898978214</v>
+        <v>65.5308194608441</v>
       </c>
       <c r="P21" s="11">
-        <v>54.9915931983244</v>
+        <v>54.4864156336232</v>
       </c>
       <c r="Q21" s="11">
-        <v>56.832500123597</v>
+        <v>57.0695227195694</v>
       </c>
       <c r="R21" s="11">
-        <v>79.3008692640183</v>
+        <v>77.2655933878037</v>
       </c>
       <c r="S21" s="11">
-        <v>34.3641309831756</v>
+        <v>36.8734520513351</v>
       </c>
       <c r="T21" s="11">
-        <v>29.4579547153139</v>
+        <v>29.9811111432412</v>
       </c>
       <c r="U21" s="11">
-        <v>25.7555810278337</v>
+        <v>26.9467958074919</v>
       </c>
       <c r="V21" s="11">
-        <v>11.8137524041682</v>
+        <v>11.026170562019</v>
       </c>
       <c r="W21" s="11">
-        <v>48.8907501419334</v>
+        <v>50.5797429161335</v>
       </c>
       <c r="X21" s="11">
         <v>31.3717352873202</v>
       </c>
       <c r="Y21" s="11">
-        <v>20.5868842474209</v>
+        <v>19.0496422467168</v>
       </c>
       <c r="Z21" s="11">
-        <v>16.1693432862591</v>
+        <v>13.7760052283139</v>
       </c>
       <c r="AA21" s="11">
-        <v>25.0044252085826</v>
+        <v>24.3232792651197</v>
       </c>
       <c r="AB21" s="11">
-        <v>35.6257796954439</v>
+        <v>35.3667587031758</v>
       </c>
       <c r="AC21" s="11">
-        <v>45.3086864468842</v>
+        <v>44.9265871683995</v>
       </c>
     </row>
     <row r="22" ht="20.05" customHeight="1">
@@ -3525,82 +3527,82 @@
         <v>69</v>
       </c>
       <c r="D22" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E22" s="11">
-        <v>43.2220179010292</v>
+        <v>42.9827662114677</v>
       </c>
       <c r="F22" s="11">
-        <v>44.6163929655269</v>
+        <v>47.1391874451769</v>
       </c>
       <c r="G22" s="11">
-        <v>41.8276428365314</v>
+        <v>38.8263449777584</v>
       </c>
       <c r="H22" s="11">
-        <v>39.5427558545835</v>
+        <v>40.9323922467528</v>
       </c>
       <c r="I22" s="11">
-        <v>43.1350266865668</v>
+        <v>43.7040861060292</v>
       </c>
       <c r="J22" s="11">
-        <v>43.3351418972596</v>
+        <v>46.2910200575838</v>
       </c>
       <c r="K22" s="11">
-        <v>53.829061736225</v>
+        <v>55.8626697251159</v>
       </c>
       <c r="L22" s="11">
         <v>17.8717930982823</v>
       </c>
       <c r="M22" s="11">
-        <v>40.7366950836366</v>
+        <v>42.3887270287352</v>
       </c>
       <c r="N22" s="11">
-        <v>35.1772867368525</v>
+        <v>37.8251779027727</v>
       </c>
       <c r="O22" s="11">
-        <v>46.2961034304206</v>
+        <v>46.9522761546977</v>
       </c>
       <c r="P22" s="11">
-        <v>41.1671562797497</v>
+        <v>42.1012951623185</v>
       </c>
       <c r="Q22" s="11">
-        <v>41.1156053961521</v>
+        <v>41.937373552275</v>
       </c>
       <c r="R22" s="11">
-        <v>16.5411146220638</v>
+        <v>15.4099345963242</v>
       </c>
       <c r="S22" s="11">
-        <v>65.6900961702403</v>
+        <v>68.4648125082258</v>
       </c>
       <c r="T22" s="11">
-        <v>59.1041332847914</v>
+        <v>57.7292753435166</v>
       </c>
       <c r="U22" s="11">
-        <v>82.8709647208688</v>
+        <v>83.23039138423199</v>
       </c>
       <c r="V22" s="11">
-        <v>60.7445884422613</v>
+        <v>56.3176477798338</v>
       </c>
       <c r="W22" s="11">
-        <v>61.2262885297797</v>
+        <v>59.7943707637447</v>
       </c>
       <c r="X22" s="11">
         <v>31.574691446256</v>
       </c>
       <c r="Y22" s="11">
-        <v>54.0758519494383</v>
+        <v>51.6721745257162</v>
       </c>
       <c r="Z22" s="11">
-        <v>48.0963524446976</v>
+        <v>44.2242046049648</v>
       </c>
       <c r="AA22" s="11">
-        <v>60.055351454179</v>
+        <v>59.1201444464676</v>
       </c>
       <c r="AB22" s="11">
-        <v>51.4318635434606</v>
+        <v>50.4462744738359</v>
       </c>
       <c r="AC22" s="11">
-        <v>46.2995099116052</v>
+        <v>46.2737848180772</v>
       </c>
     </row>
     <row r="23" ht="20.05" customHeight="1">
@@ -3614,82 +3616,82 @@
         <v>71</v>
       </c>
       <c r="D23" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E23" s="11">
-        <v>55.9375704181072</v>
+        <v>56.8278904119476</v>
       </c>
       <c r="F23" s="11">
-        <v>54.1292214499914</v>
+        <v>52.1190600745241</v>
       </c>
       <c r="G23" s="11">
-        <v>57.745919386223</v>
+        <v>61.5367207493711</v>
       </c>
       <c r="H23" s="11">
-        <v>50.1960356326097</v>
+        <v>50.2412254095296</v>
       </c>
       <c r="I23" s="11">
-        <v>58.9205930229275</v>
+        <v>54.9392435500722</v>
       </c>
       <c r="J23" s="11">
-        <v>41.8696555649103</v>
+        <v>43.5234435726644</v>
       </c>
       <c r="K23" s="11">
-        <v>48.6760389465921</v>
+        <v>51.1843595193729</v>
       </c>
       <c r="L23" s="11">
         <v>51.3178549960088</v>
       </c>
       <c r="M23" s="11">
-        <v>34.7999922990813</v>
+        <v>33.9239044222702</v>
       </c>
       <c r="N23" s="11">
-        <v>34.9928988898996</v>
+        <v>36.1507124796964</v>
       </c>
       <c r="O23" s="11">
-        <v>34.6070857082631</v>
+        <v>31.6970963648439</v>
       </c>
       <c r="P23" s="11">
-        <v>46.9778661165994</v>
+        <v>46.9976734145825</v>
       </c>
       <c r="Q23" s="11">
-        <v>48.5889302932622</v>
+        <v>49.1785895725161</v>
       </c>
       <c r="R23" s="11">
-        <v>49.8230770412133</v>
+        <v>53.9937246226134</v>
       </c>
       <c r="S23" s="11">
-        <v>47.354783545311</v>
+        <v>44.3634545224187</v>
       </c>
       <c r="T23" s="11">
-        <v>67.4972814943994</v>
+        <v>66.71609449364441</v>
       </c>
       <c r="U23" s="11">
-        <v>72.48418056338809</v>
+        <v>71.3824864225093</v>
       </c>
       <c r="V23" s="11">
-        <v>72.9911892920835</v>
+        <v>73.0066927470189</v>
       </c>
       <c r="W23" s="11">
-        <v>54.5404056743314</v>
+        <v>52.5018483572549</v>
       </c>
       <c r="X23" s="11">
         <v>69.9733504477944</v>
       </c>
       <c r="Y23" s="11">
-        <v>75.1775398906951</v>
+        <v>77.9283857088562</v>
       </c>
       <c r="Z23" s="11">
-        <v>66.42198259375191</v>
+        <v>70.4983954403955</v>
       </c>
       <c r="AA23" s="11">
-        <v>83.9330971876383</v>
+        <v>85.358375977317</v>
       </c>
       <c r="AB23" s="11">
-        <v>63.7545838927856</v>
+        <v>64.6076899250056</v>
       </c>
       <c r="AC23" s="11">
-        <v>55.3662250046925</v>
+        <v>55.802681669794</v>
       </c>
     </row>
     <row r="24" ht="20.05" customHeight="1">
@@ -3703,82 +3705,82 @@
         <v>73</v>
       </c>
       <c r="D24" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E24" s="11">
-        <v>44.7765047714294</v>
+        <v>45.8570957538771</v>
       </c>
       <c r="F24" s="11">
-        <v>37.0508964249208</v>
+        <v>34.8965733695569</v>
       </c>
       <c r="G24" s="11">
-        <v>52.5021131179381</v>
+        <v>56.8176181381974</v>
       </c>
       <c r="H24" s="11">
-        <v>40.2126218826897</v>
+        <v>41.5648466119978</v>
       </c>
       <c r="I24" s="11">
-        <v>25.7597068848629</v>
+        <v>37.6399410253882</v>
       </c>
       <c r="J24" s="11">
-        <v>37.5003474615435</v>
+        <v>32.1841481038147</v>
       </c>
       <c r="K24" s="11">
-        <v>50.3601724269383</v>
+        <v>49.205036561374</v>
       </c>
       <c r="L24" s="11">
         <v>47.2302607574142</v>
       </c>
       <c r="M24" s="11">
-        <v>57.3090267747836</v>
+        <v>58.6400508018033</v>
       </c>
       <c r="N24" s="11">
-        <v>59.346524927150</v>
+        <v>59.4229982443649</v>
       </c>
       <c r="O24" s="11">
-        <v>55.2715286224172</v>
+        <v>57.8571033592417</v>
       </c>
       <c r="P24" s="11">
-        <v>47.4327178096342</v>
+        <v>48.6873310558927</v>
       </c>
       <c r="Q24" s="11">
-        <v>49.4309911176786</v>
+        <v>46.5406930399162</v>
       </c>
       <c r="R24" s="11">
-        <v>39.0673980194887</v>
+        <v>38.5775947822824</v>
       </c>
       <c r="S24" s="11">
-        <v>59.7945842158686</v>
+        <v>54.5037912975499</v>
       </c>
       <c r="T24" s="11">
-        <v>57.9829507327457</v>
+        <v>58.3115111763218</v>
       </c>
       <c r="U24" s="11">
-        <v>40.8517329217662</v>
+        <v>39.9813055022813</v>
       </c>
       <c r="V24" s="11">
-        <v>70.8609446009052</v>
+        <v>71.23799935104471</v>
       </c>
       <c r="W24" s="11">
-        <v>67.2365019236458</v>
+        <v>69.0441163672955</v>
       </c>
       <c r="X24" s="11">
         <v>52.9826234846657</v>
       </c>
       <c r="Y24" s="11">
-        <v>33.4560080888365</v>
+        <v>32.7048945522728</v>
       </c>
       <c r="Z24" s="11">
-        <v>25.8438384959053</v>
+        <v>24.7204432464299</v>
       </c>
       <c r="AA24" s="11">
-        <v>41.0681776817678</v>
+        <v>40.6893458581156</v>
       </c>
       <c r="AB24" s="11">
-        <v>46.9566499797536</v>
+        <v>45.8523662561703</v>
       </c>
       <c r="AC24" s="11">
-        <v>47.1946838946939</v>
+        <v>47.2698486560315</v>
       </c>
     </row>
     <row r="25" ht="20.05" customHeight="1">
@@ -3792,82 +3794,82 @@
         <v>75</v>
       </c>
       <c r="D25" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E25" s="11">
-        <v>55.536280126449</v>
+        <v>56.2524070679651</v>
       </c>
       <c r="F25" s="11">
-        <v>57.4261285456897</v>
+        <v>55.4587746641221</v>
       </c>
       <c r="G25" s="11">
-        <v>53.6464317072083</v>
+        <v>57.0460394718081</v>
       </c>
       <c r="H25" s="11">
-        <v>48.6657687131814</v>
+        <v>47.3659906115738</v>
       </c>
       <c r="I25" s="11">
-        <v>45.1705453820633</v>
+        <v>38.6240357089541</v>
       </c>
       <c r="J25" s="11">
-        <v>51.3780178080115</v>
+        <v>51.8479440547684</v>
       </c>
       <c r="K25" s="11">
-        <v>52.743171664547</v>
+        <v>53.6206426844691</v>
       </c>
       <c r="L25" s="11">
         <v>45.3713399981037</v>
       </c>
       <c r="M25" s="11">
-        <v>59.3719209307951</v>
+        <v>59.3784544662832</v>
       </c>
       <c r="N25" s="11">
-        <v>65.5817886171308</v>
+        <v>65.1573162456903</v>
       </c>
       <c r="O25" s="11">
-        <v>53.1620532444593</v>
+        <v>53.5995926868762</v>
       </c>
       <c r="P25" s="11">
-        <v>54.5246565901418</v>
+        <v>54.3322840486074</v>
       </c>
       <c r="Q25" s="11">
-        <v>58.5586129627898</v>
+        <v>56.0475385241857</v>
       </c>
       <c r="R25" s="11">
-        <v>65.6071949969526</v>
+        <v>64.1306836453759</v>
       </c>
       <c r="S25" s="11">
-        <v>51.5100309286271</v>
+        <v>47.9643934029956</v>
       </c>
       <c r="T25" s="11">
-        <v>52.3012656849646</v>
+        <v>52.0922510444365</v>
       </c>
       <c r="U25" s="11">
-        <v>39.3360784291709</v>
+        <v>38.5731420509325</v>
       </c>
       <c r="V25" s="11">
-        <v>39.2959331724281</v>
+        <v>39.9338268638736</v>
       </c>
       <c r="W25" s="11">
-        <v>76.7599494655009</v>
+        <v>76.04893359018121</v>
       </c>
       <c r="X25" s="11">
         <v>53.8131016727586</v>
       </c>
       <c r="Y25" s="11">
-        <v>27.1844407259286</v>
+        <v>27.997105751184</v>
       </c>
       <c r="Z25" s="11">
-        <v>23.3390716636472</v>
+        <v>23.541023541388</v>
       </c>
       <c r="AA25" s="11">
-        <v>31.0298097882099</v>
+        <v>32.4531879609799</v>
       </c>
       <c r="AB25" s="11">
-        <v>46.014773124561</v>
+        <v>45.3789651066021</v>
       </c>
       <c r="AC25" s="11">
-        <v>50.2697148573514</v>
+        <v>49.8556245776047</v>
       </c>
     </row>
     <row r="26" ht="20.05" customHeight="1">
@@ -3881,82 +3883,82 @@
         <v>77</v>
       </c>
       <c r="D26" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E26" s="11">
-        <v>47.0234685699149</v>
+        <v>46.6990335759848</v>
       </c>
       <c r="F26" s="11">
-        <v>50.517090939790</v>
+        <v>50.534687640570</v>
       </c>
       <c r="G26" s="11">
-        <v>43.5298462000398</v>
+        <v>42.8633795113995</v>
       </c>
       <c r="H26" s="11">
-        <v>35.0530349971518</v>
+        <v>35.7692635885284</v>
       </c>
       <c r="I26" s="11">
-        <v>51.8662689348729</v>
+        <v>53.2585041864535</v>
       </c>
       <c r="J26" s="11">
-        <v>27.3756609956066</v>
+        <v>26.9775769743726</v>
       </c>
       <c r="K26" s="11">
-        <v>53.7825785166066</v>
+        <v>55.6533416517665</v>
       </c>
       <c r="L26" s="11">
         <v>7.18763154152119</v>
       </c>
       <c r="M26" s="11">
-        <v>38.3851827744187</v>
+        <v>41.4932427625225</v>
       </c>
       <c r="N26" s="11">
-        <v>42.2217860143299</v>
+        <v>46.6771442670222</v>
       </c>
       <c r="O26" s="11">
-        <v>34.5485795345075</v>
+        <v>36.3093412580228</v>
       </c>
       <c r="P26" s="11">
-        <v>40.1538954471618</v>
+        <v>41.3205133090119</v>
       </c>
       <c r="Q26" s="11">
-        <v>32.5958676102885</v>
+        <v>33.220095693832</v>
       </c>
       <c r="R26" s="11">
-        <v>4.35097509455943</v>
+        <v>5.61823620797644</v>
       </c>
       <c r="S26" s="11">
-        <v>60.8407601260175</v>
+        <v>60.8219551796875</v>
       </c>
       <c r="T26" s="11">
-        <v>61.0178124309952</v>
+        <v>59.2016964671118</v>
       </c>
       <c r="U26" s="11">
-        <v>65.0835572266803</v>
+        <v>61.7526439568881</v>
       </c>
       <c r="V26" s="11">
-        <v>74.37810098907509</v>
+        <v>72.5415908796181</v>
       </c>
       <c r="W26" s="11">
-        <v>73.61592059271651</v>
+        <v>71.5188801164323</v>
       </c>
       <c r="X26" s="11">
         <v>30.9936709155089</v>
       </c>
       <c r="Y26" s="11">
-        <v>68.3428298001859</v>
+        <v>67.806612449364</v>
       </c>
       <c r="Z26" s="11">
-        <v>87.06587308701251</v>
+        <v>85.38964964144439</v>
       </c>
       <c r="AA26" s="11">
-        <v>49.6197865133593</v>
+        <v>50.2235752572836</v>
       </c>
       <c r="AB26" s="11">
-        <v>53.9855032804898</v>
+        <v>53.4094682034359</v>
       </c>
       <c r="AC26" s="11">
-        <v>47.0696993638258</v>
+        <v>47.3649907562239</v>
       </c>
     </row>
     <row r="27" ht="20.05" customHeight="1">
@@ -3970,82 +3972,82 @@
         <v>79</v>
       </c>
       <c r="D27" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E27" s="11">
-        <v>45.8979243819718</v>
+        <v>45.5848242137994</v>
       </c>
       <c r="F27" s="11">
-        <v>32.9346112667036</v>
+        <v>34.5523016488819</v>
       </c>
       <c r="G27" s="11">
-        <v>58.861237497240</v>
+        <v>56.6173467787168</v>
       </c>
       <c r="H27" s="11">
-        <v>41.526555716594</v>
+        <v>41.0253153177</v>
       </c>
       <c r="I27" s="11">
-        <v>38.2729036019498</v>
+        <v>37.0706676821481</v>
       </c>
       <c r="J27" s="11">
-        <v>50.934030973445</v>
+        <v>50.7301091144893</v>
       </c>
       <c r="K27" s="11">
-        <v>57.905766649556</v>
+        <v>57.3069628327373</v>
       </c>
       <c r="L27" s="11">
         <v>18.9935216414251</v>
       </c>
       <c r="M27" s="11">
-        <v>60.1111588945729</v>
+        <v>63.0435346800892</v>
       </c>
       <c r="N27" s="11">
-        <v>53.7682400907622</v>
+        <v>57.3444130881968</v>
       </c>
       <c r="O27" s="11">
-        <v>66.4540776983836</v>
+        <v>68.7426562719815</v>
       </c>
       <c r="P27" s="11">
-        <v>49.1785463310462</v>
+        <v>49.8845580705295</v>
       </c>
       <c r="Q27" s="11">
-        <v>51.5136457389624</v>
+        <v>52.4273175982298</v>
       </c>
       <c r="R27" s="11">
-        <v>63.0499528540931</v>
+        <v>62.5371184691319</v>
       </c>
       <c r="S27" s="11">
-        <v>39.9773386238317</v>
+        <v>42.3175167273276</v>
       </c>
       <c r="T27" s="11">
-        <v>34.9585056150881</v>
+        <v>36.0639781053519</v>
       </c>
       <c r="U27" s="11">
-        <v>35.7423327504818</v>
+        <v>37.2119498567893</v>
       </c>
       <c r="V27" s="11">
-        <v>35.125731908816</v>
+        <v>36.2383785850002</v>
       </c>
       <c r="W27" s="11">
-        <v>44.5794826183534</v>
+        <v>46.4191087969168</v>
       </c>
       <c r="X27" s="11">
         <v>24.3864751827013</v>
       </c>
       <c r="Y27" s="11">
-        <v>37.1670759325709</v>
+        <v>39.9720058422663</v>
       </c>
       <c r="Z27" s="11">
-        <v>35.1130118683876</v>
+        <v>40.7534060117161</v>
       </c>
       <c r="AA27" s="11">
-        <v>39.2211399967542</v>
+        <v>39.1906056728166</v>
       </c>
       <c r="AB27" s="11">
-        <v>41.2130757622071</v>
+        <v>42.8211005152827</v>
       </c>
       <c r="AC27" s="11">
-        <v>45.1958110466267</v>
+        <v>46.3528292929061</v>
       </c>
     </row>
     <row r="28" ht="20.05" customHeight="1">
@@ -4059,82 +4061,82 @@
         <v>81</v>
       </c>
       <c r="D28" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E28" s="11">
-        <v>41.3618876981055</v>
+        <v>39.9804127898926</v>
       </c>
       <c r="F28" s="11">
-        <v>46.8207059304866</v>
+        <v>47.6802572963094</v>
       </c>
       <c r="G28" s="11">
-        <v>35.9030694657244</v>
+        <v>32.2805682834759</v>
       </c>
       <c r="H28" s="11">
-        <v>50.2550603826935</v>
+        <v>52.2062402664993</v>
       </c>
       <c r="I28" s="11">
-        <v>33.700352579695</v>
+        <v>40.749071742519</v>
       </c>
       <c r="J28" s="11">
-        <v>87.192764285715</v>
+        <v>84.54642133540069</v>
       </c>
       <c r="K28" s="11">
-        <v>34.3521988260729</v>
+        <v>37.7545421487863</v>
       </c>
       <c r="L28" s="11">
         <v>45.7749258392911</v>
       </c>
       <c r="M28" s="11">
-        <v>70.3464857661574</v>
+        <v>68.72500220223181</v>
       </c>
       <c r="N28" s="11">
-        <v>66.6118217167413</v>
+        <v>63.4265616358556</v>
       </c>
       <c r="O28" s="11">
-        <v>74.0811498155734</v>
+        <v>74.02344276860801</v>
       </c>
       <c r="P28" s="11">
-        <v>53.9878112823188</v>
+        <v>53.6372184195412</v>
       </c>
       <c r="Q28" s="11">
-        <v>58.9719330118799</v>
+        <v>64.7813835969893</v>
       </c>
       <c r="R28" s="11">
-        <v>77.87068131534851</v>
+        <v>79.9617018961451</v>
       </c>
       <c r="S28" s="11">
-        <v>40.0731847084112</v>
+        <v>49.6010652978335</v>
       </c>
       <c r="T28" s="11">
-        <v>23.5986862167267</v>
+        <v>24.260940178624</v>
       </c>
       <c r="U28" s="11">
-        <v>16.7241529616108</v>
+        <v>17.0722454923286</v>
       </c>
       <c r="V28" s="11">
-        <v>8.07919247092395</v>
+        <v>9.562113727115049</v>
       </c>
       <c r="W28" s="11">
-        <v>44.0163558705352</v>
+        <v>44.8343579312154</v>
       </c>
       <c r="X28" s="11">
         <v>25.5750435638369</v>
       </c>
       <c r="Y28" s="11">
-        <v>12.4069124042015</v>
+        <v>13.527930293106</v>
       </c>
       <c r="Z28" s="11">
-        <v>8.50271566713004</v>
+        <v>8.10493360583612</v>
       </c>
       <c r="AA28" s="11">
-        <v>16.311109141273</v>
+        <v>18.9509269803759</v>
       </c>
       <c r="AB28" s="11">
-        <v>31.659177210936</v>
+        <v>34.1900846895731</v>
       </c>
       <c r="AC28" s="11">
-        <v>42.8234942466274</v>
+        <v>43.9136515545572</v>
       </c>
     </row>
     <row r="29" ht="20.05" customHeight="1">
@@ -4148,82 +4150,82 @@
         <v>83</v>
       </c>
       <c r="D29" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E29" s="11">
-        <v>51.0429389284969</v>
+        <v>50.3028996928439</v>
       </c>
       <c r="F29" s="11">
-        <v>52.3446277522223</v>
+        <v>50.416622665004</v>
       </c>
       <c r="G29" s="11">
-        <v>49.7412501047716</v>
+        <v>50.1891767206837</v>
       </c>
       <c r="H29" s="11">
-        <v>46.8789902835878</v>
+        <v>47.7592828740085</v>
       </c>
       <c r="I29" s="11">
-        <v>48.055481974550</v>
+        <v>47.3737548610747</v>
       </c>
       <c r="J29" s="11">
-        <v>45.3637100878285</v>
+        <v>46.2491817494186</v>
       </c>
       <c r="K29" s="11">
-        <v>51.9763546140668</v>
+        <v>55.2937804276348</v>
       </c>
       <c r="L29" s="11">
         <v>42.1204144579058</v>
       </c>
       <c r="M29" s="11">
-        <v>49.4525618040973</v>
+        <v>50.5531220449878</v>
       </c>
       <c r="N29" s="11">
-        <v>52.9822875150253</v>
+        <v>55.0301865543062</v>
       </c>
       <c r="O29" s="11">
-        <v>45.9228360931693</v>
+        <v>46.0760575356695</v>
       </c>
       <c r="P29" s="11">
-        <v>49.1248303387274</v>
+        <v>49.5384348706134</v>
       </c>
       <c r="Q29" s="11">
-        <v>49.0207433492348</v>
+        <v>48.2303352647436</v>
       </c>
       <c r="R29" s="11">
-        <v>46.6833845909924</v>
+        <v>45.2020681308759</v>
       </c>
       <c r="S29" s="11">
-        <v>51.3581021074772</v>
+        <v>51.2586023986114</v>
       </c>
       <c r="T29" s="11">
-        <v>56.9900871266371</v>
+        <v>55.052986618424</v>
       </c>
       <c r="U29" s="11">
-        <v>38.9348741885542</v>
+        <v>40.1517225168291</v>
       </c>
       <c r="V29" s="11">
-        <v>80.3127974728374</v>
+        <v>77.599905803384</v>
       </c>
       <c r="W29" s="11">
-        <v>65.8931003517082</v>
+        <v>59.6407416600345</v>
       </c>
       <c r="X29" s="11">
         <v>42.8195764934486</v>
       </c>
       <c r="Y29" s="11">
-        <v>58.9131757191575</v>
+        <v>61.8339790181372</v>
       </c>
       <c r="Z29" s="11">
-        <v>76.9649428566827</v>
+        <v>76.7455456960696</v>
       </c>
       <c r="AA29" s="11">
-        <v>40.8614085816323</v>
+        <v>46.9224123402048</v>
       </c>
       <c r="AB29" s="11">
-        <v>54.9746687316765</v>
+        <v>55.0391003004349</v>
       </c>
       <c r="AC29" s="11">
-        <v>52.0497495352019</v>
+        <v>52.2887675855242</v>
       </c>
     </row>
     <row r="30" ht="20.05" customHeight="1">
@@ -4237,82 +4239,82 @@
         <v>85</v>
       </c>
       <c r="D30" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E30" s="11">
-        <v>48.286098840735</v>
+        <v>46.2396302084661</v>
       </c>
       <c r="F30" s="11">
-        <v>50.618448504709</v>
+        <v>50.2038009262012</v>
       </c>
       <c r="G30" s="11">
-        <v>45.9537491767611</v>
+        <v>42.2754594907311</v>
       </c>
       <c r="H30" s="11">
-        <v>56.150999722046</v>
+        <v>57.4182919135317</v>
       </c>
       <c r="I30" s="11">
-        <v>62.3882356808278</v>
+        <v>65.64530221933489</v>
       </c>
       <c r="J30" s="11">
-        <v>49.6644036306854</v>
+        <v>49.8704485990568</v>
       </c>
       <c r="K30" s="11">
-        <v>45.8230501496561</v>
+        <v>47.4291074087204</v>
       </c>
       <c r="L30" s="11">
         <v>66.72830942701481</v>
       </c>
       <c r="M30" s="11">
-        <v>53.1475393537247</v>
+        <v>52.2521088886</v>
       </c>
       <c r="N30" s="11">
-        <v>46.5917060581944</v>
+        <v>47.1668109128585</v>
       </c>
       <c r="O30" s="11">
-        <v>59.703372649255</v>
+        <v>57.3374068643415</v>
       </c>
       <c r="P30" s="11">
-        <v>52.5282126388353</v>
+        <v>51.970010336866</v>
       </c>
       <c r="Q30" s="11">
-        <v>60.9125633838634</v>
+        <v>64.93224203164689</v>
       </c>
       <c r="R30" s="11">
-        <v>66.2115442860662</v>
+        <v>68.7986297450762</v>
       </c>
       <c r="S30" s="11">
-        <v>55.6135824816606</v>
+        <v>61.0658543182175</v>
       </c>
       <c r="T30" s="11">
-        <v>44.4102915939194</v>
+        <v>45.6035464805204</v>
       </c>
       <c r="U30" s="11">
-        <v>31.9896484939716</v>
+        <v>32.1647192159494</v>
       </c>
       <c r="V30" s="11">
-        <v>38.0398837603026</v>
+        <v>40.7304094504445</v>
       </c>
       <c r="W30" s="11">
-        <v>49.5980760801519</v>
+        <v>51.5054992144363</v>
       </c>
       <c r="X30" s="11">
         <v>58.0135580412515</v>
       </c>
       <c r="Y30" s="11">
-        <v>34.5596973981889</v>
+        <v>36.1866366410082</v>
       </c>
       <c r="Z30" s="11">
-        <v>24.9427281684302</v>
+        <v>26.2277862087053</v>
       </c>
       <c r="AA30" s="11">
-        <v>44.1766666279475</v>
+        <v>46.1454870733111</v>
       </c>
       <c r="AB30" s="11">
-        <v>46.6275174586572</v>
+        <v>48.9074750510585</v>
       </c>
       <c r="AC30" s="11">
-        <v>49.5778650487462</v>
+        <v>50.4387426939622</v>
       </c>
     </row>
     <row r="31" ht="20.05" customHeight="1">
@@ -4326,82 +4328,82 @@
         <v>87</v>
       </c>
       <c r="D31" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E31" s="11">
-        <v>45.1268126931468</v>
+        <v>41.7302668014989</v>
       </c>
       <c r="F31" s="11">
-        <v>11.4905059797715</v>
+        <v>10.8500461317601</v>
       </c>
       <c r="G31" s="11">
-        <v>78.76311940652219</v>
+        <v>72.6104874712377</v>
       </c>
       <c r="H31" s="11">
-        <v>37.8073436834373</v>
+        <v>38.1606093938109</v>
       </c>
       <c r="I31" s="11">
-        <v>33.2744095392943</v>
+        <v>38.4741048095248</v>
       </c>
       <c r="J31" s="11">
-        <v>45.4631957644966</v>
+        <v>43.9687357829034</v>
       </c>
       <c r="K31" s="11">
-        <v>55.0240776838183</v>
+        <v>52.7319052366755</v>
       </c>
       <c r="L31" s="11">
         <v>17.4676917461401</v>
       </c>
       <c r="M31" s="11">
-        <v>54.2302501326203</v>
+        <v>53.6456682065223</v>
       </c>
       <c r="N31" s="11">
-        <v>44.7521428366718</v>
+        <v>46.0200624386826</v>
       </c>
       <c r="O31" s="11">
-        <v>63.7083574285687</v>
+        <v>61.271273974362</v>
       </c>
       <c r="P31" s="11">
-        <v>45.7214688364015</v>
+        <v>44.5121814672774</v>
       </c>
       <c r="Q31" s="11">
-        <v>29.0284170197333</v>
+        <v>30.568202053612</v>
       </c>
       <c r="R31" s="11">
-        <v>23.3471134242711</v>
+        <v>23.9670165482968</v>
       </c>
       <c r="S31" s="11">
-        <v>34.7097206151955</v>
+        <v>37.1693875589271</v>
       </c>
       <c r="T31" s="11">
-        <v>40.7958056943259</v>
+        <v>40.3599277081302</v>
       </c>
       <c r="U31" s="11">
-        <v>26.7401448230177</v>
+        <v>25.0019151476632</v>
       </c>
       <c r="V31" s="11">
-        <v>60.1616553742311</v>
+        <v>55.7998284608406</v>
       </c>
       <c r="W31" s="11">
-        <v>59.4748445745629</v>
+        <v>63.8313892185247</v>
       </c>
       <c r="X31" s="11">
         <v>16.8065780054921</v>
       </c>
       <c r="Y31" s="11">
-        <v>82.2188286233158</v>
+        <v>75.305220275778</v>
       </c>
       <c r="Z31" s="11">
-        <v>97.6673878401274</v>
+        <v>96.8259294878858</v>
       </c>
       <c r="AA31" s="11">
-        <v>66.7702694065042</v>
+        <v>53.7845110636702</v>
       </c>
       <c r="AB31" s="11">
-        <v>50.6810171124583</v>
+        <v>48.7444500125067</v>
       </c>
       <c r="AC31" s="11">
-        <v>48.2012429744299</v>
+        <v>46.628315739892</v>
       </c>
     </row>
     <row r="32" ht="20.05" customHeight="1">
@@ -4415,82 +4417,82 @@
         <v>89</v>
       </c>
       <c r="D32" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E32" s="11">
-        <v>45.5053894936247</v>
+        <v>47.4910304885373</v>
       </c>
       <c r="F32" s="11">
-        <v>36.4986851116678</v>
+        <v>41.2326247572521</v>
       </c>
       <c r="G32" s="11">
-        <v>54.5120938755815</v>
+        <v>53.7494362198225</v>
       </c>
       <c r="H32" s="11">
-        <v>42.3995295347339</v>
+        <v>38.4087757398215</v>
       </c>
       <c r="I32" s="11">
-        <v>38.0427502496137</v>
+        <v>21.0709529542088</v>
       </c>
       <c r="J32" s="11">
-        <v>35.1140499362406</v>
+        <v>35.6543246264961</v>
       </c>
       <c r="K32" s="11">
-        <v>65.653827254381</v>
+        <v>66.12233467988101</v>
       </c>
       <c r="L32" s="11">
         <v>30.7874906987001</v>
       </c>
       <c r="M32" s="11">
-        <v>45.7690141843996</v>
+        <v>50.4249144349104</v>
       </c>
       <c r="N32" s="11">
-        <v>43.4712289290687</v>
+        <v>43.521925676647</v>
       </c>
       <c r="O32" s="11">
-        <v>48.0667994397305</v>
+        <v>57.3279031931737</v>
       </c>
       <c r="P32" s="11">
-        <v>44.557977737586</v>
+        <v>45.4415735544231</v>
       </c>
       <c r="Q32" s="11">
-        <v>50.4001231849653</v>
+        <v>48.8511158327304</v>
       </c>
       <c r="R32" s="11">
-        <v>53.4904125543002</v>
+        <v>49.5631432409253</v>
       </c>
       <c r="S32" s="11">
-        <v>47.3098338156304</v>
+        <v>48.1390884245354</v>
       </c>
       <c r="T32" s="11">
-        <v>46.1355157020098</v>
+        <v>45.7813822160434</v>
       </c>
       <c r="U32" s="11">
-        <v>29.556771862929</v>
+        <v>31.473456975191</v>
       </c>
       <c r="V32" s="11">
-        <v>62.6617370788505</v>
+        <v>61.6022226664359</v>
       </c>
       <c r="W32" s="11">
-        <v>48.6845718020357</v>
+        <v>46.410867158323</v>
       </c>
       <c r="X32" s="11">
         <v>43.6389820642239</v>
       </c>
       <c r="Y32" s="11">
-        <v>73.5802031613858</v>
+        <v>72.52030911392021</v>
       </c>
       <c r="Z32" s="11">
-        <v>93.528359163704</v>
+        <v>92.833459434441</v>
       </c>
       <c r="AA32" s="11">
-        <v>53.6320471590675</v>
+        <v>52.2071587933994</v>
       </c>
       <c r="AB32" s="11">
-        <v>56.7052806827869</v>
+        <v>55.7176023875647</v>
       </c>
       <c r="AC32" s="11">
-        <v>50.6316292101865</v>
+        <v>50.5795879709939</v>
       </c>
     </row>
     <row r="33" ht="20.05" customHeight="1">
@@ -4504,82 +4506,82 @@
         <v>91</v>
       </c>
       <c r="D33" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E33" s="11">
-        <v>45.858948475454</v>
+        <v>44.911463416362</v>
       </c>
       <c r="F33" s="11">
-        <v>40.9887081900572</v>
+        <v>36.1358079615986</v>
       </c>
       <c r="G33" s="11">
-        <v>50.7291887608507</v>
+        <v>53.6871188711254</v>
       </c>
       <c r="H33" s="11">
-        <v>33.7065217732921</v>
+        <v>37.0542236456336</v>
       </c>
       <c r="I33" s="11">
-        <v>13.2000227063248</v>
+        <v>24.4354279350559</v>
       </c>
       <c r="J33" s="11">
-        <v>35.6660514702963</v>
+        <v>36.1708570125475</v>
       </c>
       <c r="K33" s="11">
-        <v>58.8317812784387</v>
+        <v>60.4823779968221</v>
       </c>
       <c r="L33" s="11">
         <v>27.1282316381087</v>
       </c>
       <c r="M33" s="11">
-        <v>42.8823438733094</v>
+        <v>44.0362344140776</v>
       </c>
       <c r="N33" s="11">
-        <v>60.5297089297327</v>
+        <v>61.3979845701792</v>
       </c>
       <c r="O33" s="11">
-        <v>25.234978816886</v>
+        <v>26.674484257976</v>
       </c>
       <c r="P33" s="11">
-        <v>40.8159380406852</v>
+        <v>42.0006404920244</v>
       </c>
       <c r="Q33" s="11">
-        <v>42.158290894963</v>
+        <v>43.1430552924631</v>
       </c>
       <c r="R33" s="11">
-        <v>24.3520624186463</v>
+        <v>28.5345932573747</v>
       </c>
       <c r="S33" s="11">
-        <v>59.9645193712797</v>
+        <v>57.7515173275516</v>
       </c>
       <c r="T33" s="11">
-        <v>57.9132021551301</v>
+        <v>58.4725186679182</v>
       </c>
       <c r="U33" s="11">
-        <v>37.9691895819937</v>
+        <v>38.235584505913</v>
       </c>
       <c r="V33" s="11">
-        <v>81.5218730929609</v>
+        <v>83.0017561560167</v>
       </c>
       <c r="W33" s="11">
-        <v>59.6549669000383</v>
+        <v>60.1459549642158</v>
       </c>
       <c r="X33" s="11">
         <v>52.5067790455274</v>
       </c>
       <c r="Y33" s="11">
-        <v>70.9089085461481</v>
+        <v>72.1177952916709</v>
       </c>
       <c r="Z33" s="11">
-        <v>68.1205549079251</v>
+        <v>66.8440969693486</v>
       </c>
       <c r="AA33" s="11">
-        <v>73.6972621843711</v>
+        <v>77.3914936139933</v>
       </c>
       <c r="AB33" s="11">
-        <v>56.9934671987471</v>
+        <v>57.9111230840174</v>
       </c>
       <c r="AC33" s="11">
-        <v>48.9047026197161</v>
+        <v>49.9558817880209</v>
       </c>
     </row>
     <row r="34" ht="20.05" customHeight="1">
@@ -4593,82 +4595,82 @@
         <v>93</v>
       </c>
       <c r="D34" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E34" s="11">
-        <v>43.9445771755835</v>
+        <v>44.382206718608</v>
       </c>
       <c r="F34" s="11">
-        <v>53.205717743864</v>
+        <v>54.9275956271254</v>
       </c>
       <c r="G34" s="11">
-        <v>34.683436607303</v>
+        <v>33.8368178100906</v>
       </c>
       <c r="H34" s="11">
-        <v>49.6525091444423</v>
+        <v>51.2213886568796</v>
       </c>
       <c r="I34" s="11">
-        <v>50.3790064392015</v>
+        <v>53.5520072846274</v>
       </c>
       <c r="J34" s="11">
-        <v>38.2626454986351</v>
+        <v>40.2717769476104</v>
       </c>
       <c r="K34" s="11">
-        <v>50.4028825381378</v>
+        <v>51.496268293486</v>
       </c>
       <c r="L34" s="11">
         <v>59.5655021017948</v>
       </c>
       <c r="M34" s="11">
-        <v>20.0842361131044</v>
+        <v>20.0366239131487</v>
       </c>
       <c r="N34" s="11">
-        <v>16.157532243028</v>
+        <v>13.7435974668903</v>
       </c>
       <c r="O34" s="11">
-        <v>24.0109399831808</v>
+        <v>26.3296503594072</v>
       </c>
       <c r="P34" s="11">
-        <v>37.8937741443767</v>
+        <v>38.5467397628788</v>
       </c>
       <c r="Q34" s="11">
-        <v>64.6260552091061</v>
+        <v>66.44878221038719</v>
       </c>
       <c r="R34" s="11">
-        <v>64.0530556553544</v>
+        <v>66.76603024821399</v>
       </c>
       <c r="S34" s="11">
-        <v>65.1990547628579</v>
+        <v>66.13153417256051</v>
       </c>
       <c r="T34" s="11">
-        <v>63.6398864529137</v>
+        <v>62.7198918424807</v>
       </c>
       <c r="U34" s="11">
-        <v>76.5090983848485</v>
+        <v>76.9759937810113</v>
       </c>
       <c r="V34" s="11">
-        <v>62.3330722482024</v>
+        <v>59.6180620175976</v>
       </c>
       <c r="W34" s="11">
-        <v>38.9478335748756</v>
+        <v>37.5159699675855</v>
       </c>
       <c r="X34" s="11">
         <v>76.7695416037282</v>
       </c>
       <c r="Y34" s="11">
-        <v>68.6196999221484</v>
+        <v>69.0625192497173</v>
       </c>
       <c r="Z34" s="11">
-        <v>55.7607851932574</v>
+        <v>55.3999385258424</v>
       </c>
       <c r="AA34" s="11">
-        <v>81.47861465103939</v>
+        <v>82.72509997359229</v>
       </c>
       <c r="AB34" s="11">
-        <v>65.6285471947227</v>
+        <v>66.07706443419509</v>
       </c>
       <c r="AC34" s="11">
-        <v>51.7611606695497</v>
+        <v>52.3119020985369</v>
       </c>
     </row>
     <row r="35" ht="20.05" customHeight="1">
@@ -4682,82 +4684,82 @@
         <v>95</v>
       </c>
       <c r="D35" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E35" s="11">
-        <v>60.1580143154709</v>
+        <v>58.4663574658251</v>
       </c>
       <c r="F35" s="11">
-        <v>68.25572196565599</v>
+        <v>66.62756962876421</v>
       </c>
       <c r="G35" s="11">
-        <v>52.0603066652859</v>
+        <v>50.3051453028861</v>
       </c>
       <c r="H35" s="11">
-        <v>53.121902309569</v>
+        <v>52.2877999427495</v>
       </c>
       <c r="I35" s="11">
-        <v>32.6829347924517</v>
+        <v>28.2434118042091</v>
       </c>
       <c r="J35" s="11">
-        <v>62.2879876067233</v>
+        <v>63.1316249219658</v>
       </c>
       <c r="K35" s="11">
-        <v>35.5731250187626</v>
+        <v>35.8326012244847</v>
       </c>
       <c r="L35" s="11">
         <v>81.9435618203383</v>
       </c>
       <c r="M35" s="11">
-        <v>63.093403079011</v>
+        <v>61.9948541476653</v>
       </c>
       <c r="N35" s="11">
-        <v>62.3763603429437</v>
+        <v>59.9504001939767</v>
       </c>
       <c r="O35" s="11">
-        <v>63.8104458150784</v>
+        <v>64.039308101354</v>
       </c>
       <c r="P35" s="11">
-        <v>58.791106568017</v>
+        <v>57.583003852080</v>
       </c>
       <c r="Q35" s="11">
-        <v>64.0145971226148</v>
+        <v>64.8593124163279</v>
       </c>
       <c r="R35" s="11">
-        <v>79.2948513341001</v>
+        <v>80.31720136937901</v>
       </c>
       <c r="S35" s="11">
-        <v>48.7343429111295</v>
+        <v>49.4014234632768</v>
       </c>
       <c r="T35" s="11">
-        <v>42.3178401997324</v>
+        <v>42.4544624775686</v>
       </c>
       <c r="U35" s="11">
-        <v>34.8282642287345</v>
+        <v>34.5284857255709</v>
       </c>
       <c r="V35" s="11">
-        <v>37.4502094975213</v>
+        <v>42.0289381226114</v>
       </c>
       <c r="W35" s="11">
-        <v>40.9904970877786</v>
+        <v>37.2580360771967</v>
       </c>
       <c r="X35" s="11">
         <v>56.0023899848952</v>
       </c>
       <c r="Y35" s="11">
-        <v>22.2246787021257</v>
+        <v>23.3868542481415</v>
       </c>
       <c r="Z35" s="11">
-        <v>24.8015938031848</v>
+        <v>23.6042816494732</v>
       </c>
       <c r="AA35" s="11">
-        <v>19.6477636010666</v>
+        <v>23.1694268468098</v>
       </c>
       <c r="AB35" s="11">
-        <v>42.8523720081576</v>
+        <v>43.5668763806793</v>
       </c>
       <c r="AC35" s="11">
-        <v>50.8217392880873</v>
+        <v>50.5749401163797</v>
       </c>
     </row>
     <row r="36" ht="20.05" customHeight="1">
@@ -4771,82 +4773,82 @@
         <v>97</v>
       </c>
       <c r="D36" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E36" s="11">
-        <v>52.1334480111483</v>
+        <v>47.356146499923</v>
       </c>
       <c r="F36" s="11">
-        <v>64.73658302116991</v>
+        <v>64.0888902059117</v>
       </c>
       <c r="G36" s="11">
-        <v>39.5303130011267</v>
+        <v>30.6234027939342</v>
       </c>
       <c r="H36" s="11">
-        <v>61.8320843818724</v>
+        <v>59.3793776433838</v>
       </c>
       <c r="I36" s="11">
-        <v>54.8053257535822</v>
+        <v>44.3116382925204</v>
       </c>
       <c r="J36" s="11">
-        <v>52.4781210938424</v>
+        <v>53.3585110747876</v>
       </c>
       <c r="K36" s="11">
-        <v>41.0479887507196</v>
+        <v>40.850459276882</v>
       </c>
       <c r="L36" s="11">
         <v>98.9969019293452</v>
       </c>
       <c r="M36" s="11">
-        <v>50.3732212353935</v>
+        <v>52.3847608667941</v>
       </c>
       <c r="N36" s="11">
-        <v>51.1402325055826</v>
+        <v>55.1525790973592</v>
       </c>
       <c r="O36" s="11">
-        <v>49.6062099652044</v>
+        <v>49.6169426362289</v>
       </c>
       <c r="P36" s="11">
-        <v>54.7795845428047</v>
+        <v>53.040095003367</v>
       </c>
       <c r="Q36" s="11">
-        <v>78.54506599162821</v>
+        <v>82.0818777400133</v>
       </c>
       <c r="R36" s="11">
-        <v>95.077559833141</v>
+        <v>94.91605117543629</v>
       </c>
       <c r="S36" s="11">
-        <v>62.0125721501154</v>
+        <v>69.2477043045903</v>
       </c>
       <c r="T36" s="11">
-        <v>55.3613345505402</v>
+        <v>54.2896823872647</v>
       </c>
       <c r="U36" s="11">
-        <v>54.7768124460795</v>
+        <v>55.0623971583151</v>
       </c>
       <c r="V36" s="11">
-        <v>46.4422806628679</v>
+        <v>42.7926076248107</v>
       </c>
       <c r="W36" s="11">
-        <v>21.5002332284783</v>
+        <v>20.577712901198</v>
       </c>
       <c r="X36" s="11">
         <v>98.7260118647352</v>
       </c>
       <c r="Y36" s="11">
-        <v>67.75693857987351</v>
+        <v>70.4292599493531</v>
       </c>
       <c r="Z36" s="11">
-        <v>60.8956019240536</v>
+        <v>66.1708653404592</v>
       </c>
       <c r="AA36" s="11">
-        <v>74.6182752356933</v>
+        <v>74.6876545582469</v>
       </c>
       <c r="AB36" s="11">
-        <v>67.22111304068061</v>
+        <v>68.9336066922104</v>
       </c>
       <c r="AC36" s="11">
-        <v>61.0003487917427</v>
+        <v>60.9868508477887</v>
       </c>
     </row>
     <row r="37" ht="20.05" customHeight="1">
@@ -4860,82 +4862,82 @@
         <v>99</v>
       </c>
       <c r="D37" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E37" s="11">
-        <v>45.5013474764926</v>
+        <v>46.0278938337456</v>
       </c>
       <c r="F37" s="11">
-        <v>56.3743529956739</v>
+        <v>56.1458904930564</v>
       </c>
       <c r="G37" s="11">
-        <v>34.6283419573113</v>
+        <v>35.9098971744347</v>
       </c>
       <c r="H37" s="11">
-        <v>43.461056979727</v>
+        <v>43.6688822334413</v>
       </c>
       <c r="I37" s="11">
-        <v>49.3034437698109</v>
+        <v>49.6719328154787</v>
       </c>
       <c r="J37" s="11">
-        <v>55.4262149291193</v>
+        <v>55.2935154745586</v>
       </c>
       <c r="K37" s="11">
-        <v>43.9172551432999</v>
+        <v>44.5127665670499</v>
       </c>
       <c r="L37" s="11">
         <v>25.197314076678</v>
       </c>
       <c r="M37" s="11">
-        <v>43.5911525504145</v>
+        <v>43.5763237082984</v>
       </c>
       <c r="N37" s="11">
-        <v>29.0933174140395</v>
+        <v>27.7036070426714</v>
       </c>
       <c r="O37" s="11">
-        <v>58.0889876867896</v>
+        <v>59.4490403739255</v>
       </c>
       <c r="P37" s="11">
-        <v>44.1845190022114</v>
+        <v>44.4243665918284</v>
       </c>
       <c r="Q37" s="11">
-        <v>40.5364262100494</v>
+        <v>39.2638632412194</v>
       </c>
       <c r="R37" s="11">
-        <v>13.7695357332408</v>
+        <v>12.3155628746077</v>
       </c>
       <c r="S37" s="11">
-        <v>67.303316686858</v>
+        <v>66.2121636078311</v>
       </c>
       <c r="T37" s="11">
-        <v>52.9680186375909</v>
+        <v>52.697296274223</v>
       </c>
       <c r="U37" s="11">
-        <v>99.6431297455869</v>
+        <v>99.6887875088288</v>
       </c>
       <c r="V37" s="11">
-        <v>39.1961928366212</v>
+        <v>37.8029616103183</v>
       </c>
       <c r="W37" s="11">
-        <v>50.0930516978189</v>
+        <v>50.3577357074082</v>
       </c>
       <c r="X37" s="11">
         <v>22.9397002703367</v>
       </c>
       <c r="Y37" s="11">
-        <v>34.8597246776368</v>
+        <v>33.7923046185093</v>
       </c>
       <c r="Z37" s="11">
-        <v>23.1589399540269</v>
+        <v>22.9186276272489</v>
       </c>
       <c r="AA37" s="11">
-        <v>46.5605094012467</v>
+        <v>44.6659816097697</v>
       </c>
       <c r="AB37" s="11">
-        <v>42.7880565084257</v>
+        <v>41.9178213779839</v>
       </c>
       <c r="AC37" s="11">
-        <v>43.4862877553185</v>
+        <v>43.1710939849062</v>
       </c>
     </row>
     <row r="38" ht="20.05" customHeight="1">
@@ -4949,82 +4951,82 @@
         <v>101</v>
       </c>
       <c r="D38" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E38" s="11">
-        <v>51.2319106366029</v>
+        <v>51.4463329422853</v>
       </c>
       <c r="F38" s="11">
-        <v>36.6133421374586</v>
+        <v>36.7203355819584</v>
       </c>
       <c r="G38" s="11">
-        <v>65.85047913574719</v>
+        <v>66.1723303026122</v>
       </c>
       <c r="H38" s="11">
-        <v>43.9258389415147</v>
+        <v>43.4371977751248</v>
       </c>
       <c r="I38" s="11">
-        <v>47.9775116261327</v>
+        <v>44.1903897243126</v>
       </c>
       <c r="J38" s="11">
-        <v>49.019434228855</v>
+        <v>49.3772081606841</v>
       </c>
       <c r="K38" s="11">
-        <v>53.1498527748904</v>
+        <v>54.6246360793216</v>
       </c>
       <c r="L38" s="11">
         <v>25.5565571361808</v>
       </c>
       <c r="M38" s="11">
-        <v>56.9653610576341</v>
+        <v>56.8667474721409</v>
       </c>
       <c r="N38" s="11">
-        <v>56.8660070138804</v>
+        <v>57.5218553372495</v>
       </c>
       <c r="O38" s="11">
-        <v>57.0647151013878</v>
+        <v>56.2116396070324</v>
       </c>
       <c r="P38" s="11">
-        <v>50.7077035452506</v>
+        <v>50.5834260631837</v>
       </c>
       <c r="Q38" s="11">
-        <v>44.5811492790426</v>
+        <v>44.8237826424707</v>
       </c>
       <c r="R38" s="11">
-        <v>55.8120399464779</v>
+        <v>56.490971165527</v>
       </c>
       <c r="S38" s="11">
-        <v>33.3502586116073</v>
+        <v>33.1565941194144</v>
       </c>
       <c r="T38" s="11">
-        <v>39.4935011675934</v>
+        <v>39.2115145514254</v>
       </c>
       <c r="U38" s="11">
-        <v>39.6128058317878</v>
+        <v>39.494008282788</v>
       </c>
       <c r="V38" s="11">
-        <v>32.6046679671289</v>
+        <v>32.6057277131743</v>
       </c>
       <c r="W38" s="11">
-        <v>53.6900343087535</v>
+        <v>52.6798256470361</v>
       </c>
       <c r="X38" s="11">
         <v>32.0664965627033</v>
       </c>
       <c r="Y38" s="11">
-        <v>35.534692355463</v>
+        <v>35.0678734939657</v>
       </c>
       <c r="Z38" s="11">
-        <v>39.1318787157275</v>
+        <v>38.0223495212662</v>
       </c>
       <c r="AA38" s="11">
-        <v>31.9375059951985</v>
+        <v>32.1133974666652</v>
       </c>
       <c r="AB38" s="11">
-        <v>39.869780934033</v>
+        <v>39.7010568959539</v>
       </c>
       <c r="AC38" s="11">
-        <v>45.2887422396418</v>
+        <v>45.1422414795688</v>
       </c>
     </row>
     <row r="39" ht="20.05" customHeight="1">
@@ -5038,82 +5040,82 @@
         <v>103</v>
       </c>
       <c r="D39" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E39" s="11">
-        <v>55.4247496479322</v>
+        <v>57.2961787258804</v>
       </c>
       <c r="F39" s="11">
-        <v>44.5531690806186</v>
+        <v>43.8695081563001</v>
       </c>
       <c r="G39" s="11">
-        <v>66.2963302152457</v>
+        <v>70.7228492954608</v>
       </c>
       <c r="H39" s="11">
-        <v>50.0205372225503</v>
+        <v>49.8613808572551</v>
       </c>
       <c r="I39" s="11">
-        <v>28.9216267830891</v>
+        <v>28.915839976048</v>
       </c>
       <c r="J39" s="11">
-        <v>53.1551319516883</v>
+        <v>53.6871434529452</v>
       </c>
       <c r="K39" s="11">
-        <v>45.617962347033</v>
+        <v>44.4551121916361</v>
       </c>
       <c r="L39" s="11">
         <v>72.3874278083909</v>
       </c>
       <c r="M39" s="11">
-        <v>64.0669397688513</v>
+        <v>64.98414559187169</v>
       </c>
       <c r="N39" s="11">
-        <v>65.9104739009516</v>
+        <v>67.7544670488825</v>
       </c>
       <c r="O39" s="11">
-        <v>62.223405636751</v>
+        <v>62.213824134861</v>
       </c>
       <c r="P39" s="11">
-        <v>56.5040755464446</v>
+        <v>57.3805683916691</v>
       </c>
       <c r="Q39" s="11">
-        <v>50.3512356556377</v>
+        <v>49.4136942787345</v>
       </c>
       <c r="R39" s="11">
-        <v>75.3667256350125</v>
+        <v>75.3996354593111</v>
       </c>
       <c r="S39" s="11">
-        <v>25.3357456762629</v>
+        <v>23.4277530981579</v>
       </c>
       <c r="T39" s="11">
-        <v>35.9045033596854</v>
+        <v>36.5009245093004</v>
       </c>
       <c r="U39" s="11">
-        <v>22.8493783290304</v>
+        <v>24.041369128046</v>
       </c>
       <c r="V39" s="11">
-        <v>37.9647557028425</v>
+        <v>39.0085682657259</v>
       </c>
       <c r="W39" s="11">
-        <v>35.3858993882963</v>
+        <v>35.5357806248571</v>
       </c>
       <c r="X39" s="11">
         <v>47.4179800185725</v>
       </c>
       <c r="Y39" s="11">
-        <v>45.9191208089566</v>
+        <v>45.0627878809192</v>
       </c>
       <c r="Z39" s="11">
-        <v>47.1422954708203</v>
+        <v>48.3076256595861</v>
       </c>
       <c r="AA39" s="11">
-        <v>44.6959461470928</v>
+        <v>41.8179501022523</v>
       </c>
       <c r="AB39" s="11">
-        <v>44.0582866080932</v>
+        <v>43.659135556318</v>
       </c>
       <c r="AC39" s="11">
-        <v>50.2811810772689</v>
+        <v>50.5198519739936</v>
       </c>
     </row>
     <row r="40" ht="20.05" customHeight="1">
@@ -5127,82 +5129,82 @@
         <v>105</v>
       </c>
       <c r="D40" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E40" s="11">
-        <v>52.9496979051943</v>
+        <v>50.4458488732798</v>
       </c>
       <c r="F40" s="11">
-        <v>67.1000173905614</v>
+        <v>64.76627139486411</v>
       </c>
       <c r="G40" s="11">
-        <v>38.7993784198272</v>
+        <v>36.1254263516954</v>
       </c>
       <c r="H40" s="11">
-        <v>50.3471091069874</v>
+        <v>48.0624701285388</v>
       </c>
       <c r="I40" s="11">
-        <v>72.1808648541362</v>
+        <v>65.3533387823278</v>
       </c>
       <c r="J40" s="11">
-        <v>30.0593157929229</v>
+        <v>28.8632630408181</v>
       </c>
       <c r="K40" s="11">
-        <v>46.9498959555786</v>
+        <v>45.8349188656976</v>
       </c>
       <c r="L40" s="11">
         <v>52.1983598253119</v>
       </c>
       <c r="M40" s="11">
-        <v>51.2871985360753</v>
+        <v>49.1001289131794</v>
       </c>
       <c r="N40" s="11">
-        <v>57.1717552048055</v>
+        <v>58.7253893410122</v>
       </c>
       <c r="O40" s="11">
-        <v>45.402641867345</v>
+        <v>39.4748684853465</v>
       </c>
       <c r="P40" s="11">
-        <v>51.528001849419</v>
+        <v>49.202815971666</v>
       </c>
       <c r="Q40" s="11">
-        <v>47.7239209834943</v>
+        <v>46.5461339452306</v>
       </c>
       <c r="R40" s="11">
-        <v>27.3952089623773</v>
+        <v>25.1462660978744</v>
       </c>
       <c r="S40" s="11">
-        <v>68.05263300461139</v>
+        <v>67.9460017925868</v>
       </c>
       <c r="T40" s="11">
-        <v>67.1293747160877</v>
+        <v>68.36081280628839</v>
       </c>
       <c r="U40" s="11">
-        <v>69.2396957384537</v>
+        <v>69.4574457585049</v>
       </c>
       <c r="V40" s="11">
-        <v>72.53976251759801</v>
+        <v>71.4055101032483</v>
       </c>
       <c r="W40" s="11">
-        <v>56.7390970795097</v>
+        <v>62.5813518346112</v>
       </c>
       <c r="X40" s="11">
         <v>69.9989435287894</v>
       </c>
       <c r="Y40" s="11">
-        <v>51.3156749034215</v>
+        <v>51.1819946506247</v>
       </c>
       <c r="Z40" s="11">
-        <v>56.7389182176854</v>
+        <v>56.0601415869433</v>
       </c>
       <c r="AA40" s="11">
-        <v>45.8924315891575</v>
+        <v>46.3038477143061</v>
       </c>
       <c r="AB40" s="11">
-        <v>55.3896568676678</v>
+        <v>55.3629804673813</v>
       </c>
       <c r="AC40" s="11">
-        <v>53.4588293585434</v>
+        <v>52.2828982195236</v>
       </c>
     </row>
     <row r="41" ht="20.05" customHeight="1">
@@ -5216,82 +5218,82 @@
         <v>107</v>
       </c>
       <c r="D41" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E41" s="11">
-        <v>49.6132024068916</v>
+        <v>48.0490042134739</v>
       </c>
       <c r="F41" s="11">
-        <v>32.6661965564507</v>
+        <v>32.8718773713121</v>
       </c>
       <c r="G41" s="11">
-        <v>66.5602082573325</v>
+        <v>63.2261310556358</v>
       </c>
       <c r="H41" s="11">
-        <v>44.6793272066054</v>
+        <v>44.4454546297779</v>
       </c>
       <c r="I41" s="11">
-        <v>56.1963649894659</v>
+        <v>56.9470685308266</v>
       </c>
       <c r="J41" s="11">
-        <v>40.0447382340551</v>
+        <v>39.3763157797242</v>
       </c>
       <c r="K41" s="11">
-        <v>54.3504968692929</v>
+        <v>53.332725474953</v>
       </c>
       <c r="L41" s="11">
         <v>28.1257087336079</v>
       </c>
       <c r="M41" s="11">
-        <v>54.895675635762</v>
+        <v>54.9349326320479</v>
       </c>
       <c r="N41" s="11">
-        <v>54.6034850856697</v>
+        <v>53.2781128278405</v>
       </c>
       <c r="O41" s="11">
-        <v>55.1878661858544</v>
+        <v>56.5917524362553</v>
       </c>
       <c r="P41" s="11">
-        <v>49.729401749753</v>
+        <v>49.1431304917666</v>
       </c>
       <c r="Q41" s="11">
-        <v>36.7342179036368</v>
+        <v>37.3858304397257</v>
       </c>
       <c r="R41" s="11">
-        <v>40.0397237430432</v>
+        <v>39.1394172627538</v>
       </c>
       <c r="S41" s="11">
-        <v>33.4287120642304</v>
+        <v>35.6322436166976</v>
       </c>
       <c r="T41" s="11">
-        <v>50.2461747761539</v>
+        <v>50.4259419139454</v>
       </c>
       <c r="U41" s="11">
-        <v>67.30603418507989</v>
+        <v>66.8006923363597</v>
       </c>
       <c r="V41" s="11">
-        <v>40.4825685035064</v>
+        <v>42.4128672855453</v>
       </c>
       <c r="W41" s="11">
-        <v>67.5437378724036</v>
+        <v>66.837849490251</v>
       </c>
       <c r="X41" s="11">
         <v>25.6523585436256</v>
       </c>
       <c r="Y41" s="11">
-        <v>40.2580521608933</v>
+        <v>39.8845163737244</v>
       </c>
       <c r="Z41" s="11">
-        <v>38.8519845455726</v>
+        <v>37.5546251889916</v>
       </c>
       <c r="AA41" s="11">
-        <v>41.664119776214</v>
+        <v>42.2144075584573</v>
       </c>
       <c r="AB41" s="11">
-        <v>42.4128149468947</v>
+        <v>42.5654295757985</v>
       </c>
       <c r="AC41" s="11">
-        <v>46.0711083483238</v>
+        <v>45.8542800337825</v>
       </c>
     </row>
     <row r="42" ht="20.05" customHeight="1">
@@ -5305,7 +5307,7 @@
         <v>109</v>
       </c>
       <c r="D42" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E42" t="s" s="10">
         <v>110</v>
@@ -5320,25 +5322,25 @@
         <v>110</v>
       </c>
       <c r="I42" s="11">
-        <v>31.8347182163061</v>
+        <v>37.1056446933632</v>
       </c>
       <c r="J42" s="11">
-        <v>82.2188913352233</v>
+        <v>81.31470419195109</v>
       </c>
       <c r="K42" s="11">
-        <v>39.5647816546237</v>
+        <v>38.5155862766837</v>
       </c>
       <c r="L42" t="s" s="10">
         <v>110</v>
       </c>
       <c r="M42" s="11">
-        <v>68.0696675075457</v>
+        <v>67.2553270421036</v>
       </c>
       <c r="N42" s="11">
-        <v>49.9987341444773</v>
+        <v>49.0836281949499</v>
       </c>
       <c r="O42" s="11">
-        <v>86.14060087061409</v>
+        <v>85.42702588925739</v>
       </c>
       <c r="P42" t="s" s="10">
         <v>110</v>
@@ -5356,25 +5358,25 @@
         <v>110</v>
       </c>
       <c r="U42" s="11">
-        <v>20.8589505871004</v>
+        <v>19.435162477440</v>
       </c>
       <c r="V42" s="11">
-        <v>12.0226792313937</v>
+        <v>11.5625138440474</v>
       </c>
       <c r="W42" s="11">
-        <v>39.8207887952673</v>
+        <v>44.8866550209096</v>
       </c>
       <c r="X42" t="s" s="10">
         <v>110</v>
       </c>
       <c r="Y42" s="11">
-        <v>3.1101603261754</v>
+        <v>3.76749683196731</v>
       </c>
       <c r="Z42" s="11">
-        <v>6.13372634866443</v>
+        <v>7.47964617433974</v>
       </c>
       <c r="AA42" s="11">
-        <v>0.08659430368637069</v>
+        <v>0.0553474895948872</v>
       </c>
       <c r="AB42" t="s" s="10">
         <v>110</v>
@@ -5394,82 +5396,82 @@
         <v>112</v>
       </c>
       <c r="D43" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E43" s="11">
-        <v>49.5144292417203</v>
+        <v>48.8846409332734</v>
       </c>
       <c r="F43" s="11">
-        <v>33.5756491101584</v>
+        <v>31.4194834265812</v>
       </c>
       <c r="G43" s="11">
-        <v>65.45320937328211</v>
+        <v>66.3497984399657</v>
       </c>
       <c r="H43" s="11">
-        <v>47.4795146996025</v>
+        <v>47.5842322364912</v>
       </c>
       <c r="I43" s="11">
-        <v>72.6260172087683</v>
+        <v>72.9225728225075</v>
       </c>
       <c r="J43" s="11">
-        <v>59.2441901847147</v>
+        <v>58.3864750910399</v>
       </c>
       <c r="K43" s="11">
-        <v>51.9666319781984</v>
+        <v>52.9466616056886</v>
       </c>
       <c r="L43" s="11">
         <v>6.08121942672869</v>
       </c>
       <c r="M43" s="11">
-        <v>52.9381365886185</v>
+        <v>48.7421866385392</v>
       </c>
       <c r="N43" s="11">
-        <v>55.814910537826</v>
+        <v>53.604522914467</v>
       </c>
       <c r="O43" s="11">
-        <v>50.0613626394111</v>
+        <v>43.8798503626113</v>
       </c>
       <c r="P43" s="11">
-        <v>49.9773601766471</v>
+        <v>48.4036866027679</v>
       </c>
       <c r="Q43" s="11">
-        <v>26.0827926709898</v>
+        <v>27.341656171513</v>
       </c>
       <c r="R43" s="11">
-        <v>6.90001588303836</v>
+        <v>9.934679232510449</v>
       </c>
       <c r="S43" s="11">
-        <v>45.2655694589413</v>
+        <v>44.7486331105156</v>
       </c>
       <c r="T43" s="11">
-        <v>34.494912968099</v>
+        <v>37.2137123848319</v>
       </c>
       <c r="U43" s="11">
-        <v>40.8510984315089</v>
+        <v>43.3905646900738</v>
       </c>
       <c r="V43" s="11">
-        <v>36.7557561332787</v>
+        <v>39.2551393952744</v>
       </c>
       <c r="W43" s="11">
-        <v>50.1556593235421</v>
+        <v>55.9920074699132</v>
       </c>
       <c r="X43" s="11">
         <v>10.2171379840663</v>
       </c>
       <c r="Y43" s="11">
-        <v>51.902114115340</v>
+        <v>50.6743971438019</v>
       </c>
       <c r="Z43" s="11">
-        <v>45.9056667911344</v>
+        <v>51.8973679939837</v>
       </c>
       <c r="AA43" s="11">
-        <v>57.8985614395455</v>
+        <v>49.4514262936201</v>
       </c>
       <c r="AB43" s="11">
-        <v>37.4932732514763</v>
+        <v>38.4099219000489</v>
       </c>
       <c r="AC43" s="11">
-        <v>43.7353167140617</v>
+        <v>43.4068042514084</v>
       </c>
     </row>
     <row r="44" ht="20.05" customHeight="1">
@@ -5483,82 +5485,82 @@
         <v>114</v>
       </c>
       <c r="D44" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E44" s="11">
-        <v>37.1635308022502</v>
+        <v>38.7081750625239</v>
       </c>
       <c r="F44" s="11">
-        <v>53.4465587721185</v>
+        <v>52.350880494787</v>
       </c>
       <c r="G44" s="11">
-        <v>20.880502832382</v>
+        <v>25.0654696302608</v>
       </c>
       <c r="H44" s="11">
-        <v>56.1406347440148</v>
+        <v>57.3701452956248</v>
       </c>
       <c r="I44" s="11">
-        <v>41.8621865164145</v>
+        <v>49.7193376978846</v>
       </c>
       <c r="J44" s="11">
-        <v>69.1666844371622</v>
+        <v>67.88582373540901</v>
       </c>
       <c r="K44" s="11">
-        <v>50.0676773953784</v>
+        <v>48.4094291221014</v>
       </c>
       <c r="L44" s="11">
         <v>63.4659906271042</v>
       </c>
       <c r="M44" s="11">
-        <v>54.7209778739558</v>
+        <v>56.5425176880499</v>
       </c>
       <c r="N44" s="11">
-        <v>53.1346674331161</v>
+        <v>56.9519909383663</v>
       </c>
       <c r="O44" s="11">
-        <v>56.3072883147955</v>
+        <v>56.1330444377335</v>
       </c>
       <c r="P44" s="11">
-        <v>49.3417144734069</v>
+        <v>50.8736126820662</v>
       </c>
       <c r="Q44" s="11">
-        <v>75.300908603946</v>
+        <v>74.1251974881567</v>
       </c>
       <c r="R44" s="11">
-        <v>76.26080414114141</v>
+        <v>76.7053851288611</v>
       </c>
       <c r="S44" s="11">
-        <v>74.34101306675061</v>
+        <v>71.54500984745241</v>
       </c>
       <c r="T44" s="11">
-        <v>38.5881185917513</v>
+        <v>39.371950492855</v>
       </c>
       <c r="U44" s="11">
-        <v>23.7564285333105</v>
+        <v>23.347908741847</v>
       </c>
       <c r="V44" s="11">
-        <v>30.8171259995371</v>
+        <v>31.4251678593624</v>
       </c>
       <c r="W44" s="11">
-        <v>51.9082638319752</v>
+        <v>54.8440693680283</v>
       </c>
       <c r="X44" s="11">
         <v>47.8706560021824</v>
       </c>
       <c r="Y44" s="11">
-        <v>34.6935438852558</v>
+        <v>36.831663785669</v>
       </c>
       <c r="Z44" s="11">
-        <v>21.6940160458147</v>
+        <v>25.1432152740909</v>
       </c>
       <c r="AA44" s="11">
-        <v>47.6930717246969</v>
+        <v>48.520112297247</v>
       </c>
       <c r="AB44" s="11">
-        <v>49.527523693651</v>
+        <v>50.1096039222269</v>
       </c>
       <c r="AC44" s="11">
-        <v>49.434619083529</v>
+        <v>50.4916083021465</v>
       </c>
     </row>
     <row r="45" ht="20.05" customHeight="1">
@@ -5572,82 +5574,82 @@
         <v>116</v>
       </c>
       <c r="D45" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E45" s="11">
-        <v>65.1566805501882</v>
+        <v>66.6304796047269</v>
       </c>
       <c r="F45" s="11">
-        <v>47.2843457668398</v>
+        <v>47.6538689562387</v>
       </c>
       <c r="G45" s="11">
-        <v>83.02901533353671</v>
+        <v>85.6070902532152</v>
       </c>
       <c r="H45" s="11">
-        <v>39.5462361285166</v>
+        <v>37.305635969347</v>
       </c>
       <c r="I45" s="11">
-        <v>45.1288931314682</v>
+        <v>40.902557907040</v>
       </c>
       <c r="J45" s="11">
-        <v>49.8825840414056</v>
+        <v>49.2398671748161</v>
       </c>
       <c r="K45" s="11">
-        <v>57.8226982280311</v>
+        <v>53.7293496823703</v>
       </c>
       <c r="L45" s="11">
         <v>5.35076911316155</v>
       </c>
       <c r="M45" s="11">
-        <v>45.5104278404117</v>
+        <v>47.711207250064</v>
       </c>
       <c r="N45" s="11">
-        <v>41.5425791834273</v>
+        <v>44.4440160759696</v>
       </c>
       <c r="O45" s="11">
-        <v>49.4782764973961</v>
+        <v>50.9783984241583</v>
       </c>
       <c r="P45" s="11">
-        <v>50.0711148397055</v>
+        <v>50.549107608046</v>
       </c>
       <c r="Q45" s="11">
-        <v>9.939011130909529</v>
+        <v>9.486551883205109</v>
       </c>
       <c r="R45" s="11">
-        <v>4.28584695715801</v>
+        <v>4.68443183280714</v>
       </c>
       <c r="S45" s="11">
-        <v>15.5921753046611</v>
+        <v>14.2886719336031</v>
       </c>
       <c r="T45" s="11">
-        <v>39.1736196348682</v>
+        <v>39.7923082582776</v>
       </c>
       <c r="U45" s="11">
-        <v>35.6511911435733</v>
+        <v>34.0306422565136</v>
       </c>
       <c r="V45" s="11">
-        <v>59.7431550670899</v>
+        <v>62.6590586715945</v>
       </c>
       <c r="W45" s="11">
-        <v>55.2147945785933</v>
+        <v>56.394194354786</v>
       </c>
       <c r="X45" s="11">
         <v>6.08533775021626</v>
       </c>
       <c r="Y45" s="11">
-        <v>66.11550536560689</v>
+        <v>66.41526627040059</v>
       </c>
       <c r="Z45" s="11">
-        <v>91.0797097357476</v>
+        <v>91.7244112090991</v>
       </c>
       <c r="AA45" s="11">
-        <v>41.1513009954662</v>
+        <v>41.1061213317022</v>
       </c>
       <c r="AB45" s="11">
-        <v>38.4093787104615</v>
+        <v>38.5647088039611</v>
       </c>
       <c r="AC45" s="11">
-        <v>44.2402467750835</v>
+        <v>44.5569082060035</v>
       </c>
     </row>
     <row r="46" ht="20.05" customHeight="1">
@@ -5661,82 +5663,82 @@
         <v>118</v>
       </c>
       <c r="D46" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E46" s="11">
-        <v>50.4377995019135</v>
+        <v>48.3307709242355</v>
       </c>
       <c r="F46" s="11">
-        <v>55.8341116324709</v>
+        <v>57.0699594769164</v>
       </c>
       <c r="G46" s="11">
-        <v>45.0414873713562</v>
+        <v>39.5915823715545</v>
       </c>
       <c r="H46" s="11">
-        <v>52.4405637251996</v>
+        <v>52.2544502843702</v>
       </c>
       <c r="I46" s="11">
-        <v>52.4514343189209</v>
+        <v>53.6539892109897</v>
       </c>
       <c r="J46" s="11">
-        <v>63.0426641255517</v>
+        <v>63.3958933186881</v>
       </c>
       <c r="K46" s="11">
-        <v>52.6741223997283</v>
+        <v>50.3738845512052</v>
       </c>
       <c r="L46" s="11">
         <v>41.5940340565976</v>
       </c>
       <c r="M46" s="11">
-        <v>59.5695069028885</v>
+        <v>55.9794673999399</v>
       </c>
       <c r="N46" s="11">
-        <v>49.3121089860831</v>
+        <v>47.656304303718</v>
       </c>
       <c r="O46" s="11">
-        <v>69.82690481969379</v>
+        <v>64.3026304961618</v>
       </c>
       <c r="P46" s="11">
-        <v>54.1492900433339</v>
+        <v>52.1882295361818</v>
       </c>
       <c r="Q46" s="11">
-        <v>66.0664480727598</v>
+        <v>67.9861321891424</v>
       </c>
       <c r="R46" s="11">
-        <v>78.9149457967315</v>
+        <v>77.8403680125175</v>
       </c>
       <c r="S46" s="11">
-        <v>53.2179503487882</v>
+        <v>58.1318963657672</v>
       </c>
       <c r="T46" s="11">
-        <v>32.4622398815589</v>
+        <v>32.9456481987662</v>
       </c>
       <c r="U46" s="11">
-        <v>25.4091952668394</v>
+        <v>25.8728086894643</v>
       </c>
       <c r="V46" s="11">
-        <v>21.5364353524012</v>
+        <v>23.9599810272245</v>
       </c>
       <c r="W46" s="11">
-        <v>43.0358111232664</v>
+        <v>42.0822852946474</v>
       </c>
       <c r="X46" s="11">
         <v>39.8675177837287</v>
       </c>
       <c r="Y46" s="11">
-        <v>32.3699300334553</v>
+        <v>32.9007808210381</v>
       </c>
       <c r="Z46" s="11">
-        <v>21.5356480076654</v>
+        <v>22.6384527500639</v>
       </c>
       <c r="AA46" s="11">
-        <v>43.2042120592453</v>
+        <v>43.1631088920123</v>
       </c>
       <c r="AB46" s="11">
-        <v>43.6328726625914</v>
+        <v>44.6108537363156</v>
       </c>
       <c r="AC46" s="11">
-        <v>48.8910813529626</v>
+        <v>48.3995416362487</v>
       </c>
     </row>
     <row r="47" ht="20.05" customHeight="1">
@@ -5750,82 +5752,82 @@
         <v>120</v>
       </c>
       <c r="D47" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E47" s="11">
-        <v>55.8897174034031</v>
+        <v>56.4235025355531</v>
       </c>
       <c r="F47" s="11">
-        <v>48.1745694033947</v>
+        <v>46.7854313366009</v>
       </c>
       <c r="G47" s="11">
-        <v>63.6048654034114</v>
+        <v>66.0615737345054</v>
       </c>
       <c r="H47" s="11">
-        <v>55.0583158098859</v>
+        <v>55.5960007229351</v>
       </c>
       <c r="I47" s="11">
-        <v>52.389290087436</v>
+        <v>52.7223390675107</v>
       </c>
       <c r="J47" s="11">
-        <v>53.4696424662224</v>
+        <v>54.3769277221926</v>
       </c>
       <c r="K47" s="11">
-        <v>40.4542502658413</v>
+        <v>41.3646556819931</v>
       </c>
       <c r="L47" s="11">
         <v>73.920080420044</v>
       </c>
       <c r="M47" s="11">
-        <v>48.8171422047678</v>
+        <v>47.7234229495996</v>
       </c>
       <c r="N47" s="11">
-        <v>44.3895100185784</v>
+        <v>45.5412248544871</v>
       </c>
       <c r="O47" s="11">
-        <v>53.2447743909573</v>
+        <v>49.9056210447122</v>
       </c>
       <c r="P47" s="11">
-        <v>53.2550584726856</v>
+        <v>53.2476420693626</v>
       </c>
       <c r="Q47" s="11">
-        <v>57.7956634336984</v>
+        <v>55.8566550701899</v>
       </c>
       <c r="R47" s="11">
-        <v>79.1981126700245</v>
+        <v>77.86651170004311</v>
       </c>
       <c r="S47" s="11">
-        <v>36.3932141973722</v>
+        <v>33.8467984403367</v>
       </c>
       <c r="T47" s="11">
-        <v>37.955510893562</v>
+        <v>38.1589198366409</v>
       </c>
       <c r="U47" s="11">
-        <v>36.9977874638116</v>
+        <v>38.5598084696205</v>
       </c>
       <c r="V47" s="11">
-        <v>31.9926799122988</v>
+        <v>30.8326228917073</v>
       </c>
       <c r="W47" s="11">
-        <v>14.4898156958818</v>
+        <v>14.9014874829798</v>
       </c>
       <c r="X47" s="11">
         <v>68.34176050225589</v>
       </c>
       <c r="Y47" s="11">
-        <v>63.0676208547674</v>
+        <v>63.0830526590898</v>
       </c>
       <c r="Z47" s="11">
-        <v>70.99491639496991</v>
+        <v>71.0689546664414</v>
       </c>
       <c r="AA47" s="11">
-        <v>55.140325314565</v>
+        <v>55.0971506517383</v>
       </c>
       <c r="AB47" s="11">
-        <v>52.9395983940093</v>
+        <v>52.3662091886402</v>
       </c>
       <c r="AC47" s="11">
-        <v>53.0973284333474</v>
+        <v>52.8069256290014</v>
       </c>
     </row>
     <row r="48" ht="20.05" customHeight="1">
@@ -5839,82 +5841,82 @@
         <v>122</v>
       </c>
       <c r="D48" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E48" s="11">
-        <v>53.3427962917581</v>
+        <v>53.0076504816103</v>
       </c>
       <c r="F48" s="11">
-        <v>53.2669125995598</v>
+        <v>52.969809156489</v>
       </c>
       <c r="G48" s="11">
-        <v>53.4186799839564</v>
+        <v>53.0454918067316</v>
       </c>
       <c r="H48" s="11">
-        <v>48.8616455420237</v>
+        <v>50.114863480694</v>
       </c>
       <c r="I48" s="11">
-        <v>49.6224319339936</v>
+        <v>54.2509193070074</v>
       </c>
       <c r="J48" s="11">
-        <v>48.3997601244625</v>
+        <v>48.1835008436011</v>
       </c>
       <c r="K48" s="11">
-        <v>48.4414397459835</v>
+        <v>49.0420834085121</v>
       </c>
       <c r="L48" s="11">
         <v>48.9829503636553</v>
       </c>
       <c r="M48" s="11">
-        <v>45.9485483379582</v>
+        <v>45.6616615542649</v>
       </c>
       <c r="N48" s="11">
-        <v>41.7778509702776</v>
+        <v>41.5776689726196</v>
       </c>
       <c r="O48" s="11">
-        <v>50.1192457056388</v>
+        <v>49.7456541359102</v>
       </c>
       <c r="P48" s="11">
-        <v>49.3843300572467</v>
+        <v>49.5947251721897</v>
       </c>
       <c r="Q48" s="11">
-        <v>50.5363349496997</v>
+        <v>50.7311345851342</v>
       </c>
       <c r="R48" s="11">
-        <v>53.8702837921366</v>
+        <v>54.0210626690257</v>
       </c>
       <c r="S48" s="11">
-        <v>47.2023861072628</v>
+        <v>47.4412065012427</v>
       </c>
       <c r="T48" s="11">
-        <v>47.8604781330472</v>
+        <v>47.7103901347593</v>
       </c>
       <c r="U48" s="11">
-        <v>53.9086937371208</v>
+        <v>54.247678643684</v>
       </c>
       <c r="V48" s="11">
-        <v>43.0999934268465</v>
+        <v>42.3094345479738</v>
       </c>
       <c r="W48" s="11">
-        <v>41.3203265984369</v>
+        <v>41.1715485775949</v>
       </c>
       <c r="X48" s="11">
         <v>53.1128987697845</v>
       </c>
       <c r="Y48" s="11">
-        <v>47.8412694885383</v>
+        <v>47.9318322619671</v>
       </c>
       <c r="Z48" s="11">
-        <v>43.8851820683209</v>
+        <v>44.0156205040456</v>
       </c>
       <c r="AA48" s="11">
-        <v>51.7973569087558</v>
+        <v>51.8480440198885</v>
       </c>
       <c r="AB48" s="11">
-        <v>48.7460275237617</v>
+        <v>48.7911189939535</v>
       </c>
       <c r="AC48" s="11">
-        <v>49.0651787905042</v>
+        <v>49.1929220830716</v>
       </c>
     </row>
     <row r="49" ht="20.05" customHeight="1">
@@ -5928,82 +5930,82 @@
         <v>124</v>
       </c>
       <c r="D49" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E49" s="11">
-        <v>62.6072085522108</v>
+        <v>61.0708853728962</v>
       </c>
       <c r="F49" s="11">
-        <v>68.809712140134</v>
+        <v>69.8950186720151</v>
       </c>
       <c r="G49" s="11">
-        <v>56.4047049642877</v>
+        <v>52.2467520737774</v>
       </c>
       <c r="H49" s="11">
-        <v>61.0532372391446</v>
+        <v>60.0646784381638</v>
       </c>
       <c r="I49" s="11">
-        <v>47.9943470154438</v>
+        <v>45.3295504479105</v>
       </c>
       <c r="J49" s="11">
-        <v>40.3338425445629</v>
+        <v>38.876223441743</v>
       </c>
       <c r="K49" s="11">
-        <v>60.2779210250739</v>
+        <v>60.4461014915037</v>
       </c>
       <c r="L49" s="11">
         <v>95.6068383714978</v>
       </c>
       <c r="M49" s="11">
-        <v>49.1553987309009</v>
+        <v>48.7330406119522</v>
       </c>
       <c r="N49" s="11">
-        <v>57.3072306335172</v>
+        <v>59.8783823359205</v>
       </c>
       <c r="O49" s="11">
-        <v>41.0035668282847</v>
+        <v>37.5876988879838</v>
       </c>
       <c r="P49" s="11">
-        <v>57.6052815074188</v>
+        <v>56.6228681410041</v>
       </c>
       <c r="Q49" s="11">
-        <v>66.05528583571871</v>
+        <v>65.70492553084679</v>
       </c>
       <c r="R49" s="11">
-        <v>72.5306471526642</v>
+        <v>68.5177360510268</v>
       </c>
       <c r="S49" s="11">
-        <v>59.5799245187733</v>
+        <v>62.8921150106668</v>
       </c>
       <c r="T49" s="11">
-        <v>72.3531056477061</v>
+        <v>72.4815786452603</v>
       </c>
       <c r="U49" s="11">
-        <v>55.4849757121029</v>
+        <v>57.121430323286</v>
       </c>
       <c r="V49" s="11">
-        <v>85.9918163337678</v>
+        <v>84.78867869460301</v>
       </c>
       <c r="W49" s="11">
-        <v>49.8618654491513</v>
+        <v>49.9424404673498</v>
       </c>
       <c r="X49" s="11">
         <v>98.0737650958025</v>
       </c>
       <c r="Y49" s="11">
-        <v>78.9406808249838</v>
+        <v>78.15904197731879</v>
       </c>
       <c r="Z49" s="11">
-        <v>91.1705124922152</v>
+        <v>88.668068071956</v>
       </c>
       <c r="AA49" s="11">
-        <v>66.71084915775241</v>
+        <v>67.6500158826815</v>
       </c>
       <c r="AB49" s="11">
-        <v>72.4496907694695</v>
+        <v>72.115182051142</v>
       </c>
       <c r="AC49" s="11">
-        <v>65.0274861384442</v>
+        <v>64.369025096073</v>
       </c>
     </row>
     <row r="50" ht="20.05" customHeight="1">
@@ -6017,82 +6019,82 @@
         <v>126</v>
       </c>
       <c r="D50" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E50" s="11">
-        <v>48.7677311356844</v>
+        <v>48.5770040373846</v>
       </c>
       <c r="F50" s="11">
-        <v>48.6122861049607</v>
+        <v>49.1488438655271</v>
       </c>
       <c r="G50" s="11">
-        <v>48.9231761664081</v>
+        <v>48.0051642092422</v>
       </c>
       <c r="H50" s="11">
-        <v>48.513700813247</v>
+        <v>49.0599118582512</v>
       </c>
       <c r="I50" s="11">
-        <v>55.044471496878</v>
+        <v>56.8639871354423</v>
       </c>
       <c r="J50" s="11">
-        <v>39.3504189095891</v>
+        <v>38.0033424422345</v>
       </c>
       <c r="K50" s="11">
-        <v>48.8774808576513</v>
+        <v>50.5898858664583</v>
       </c>
       <c r="L50" s="11">
         <v>50.7824319888696</v>
       </c>
       <c r="M50" s="11">
-        <v>39.3368751002731</v>
+        <v>38.7998007264627</v>
       </c>
       <c r="N50" s="11">
-        <v>39.4820359088857</v>
+        <v>41.0063403248006</v>
       </c>
       <c r="O50" s="11">
-        <v>39.1917142916606</v>
+        <v>36.5932611281249</v>
       </c>
       <c r="P50" s="11">
-        <v>45.5394356830682</v>
+        <v>45.4789055406995</v>
       </c>
       <c r="Q50" s="11">
-        <v>56.8930574205274</v>
+        <v>57.7616267225592</v>
       </c>
       <c r="R50" s="11">
-        <v>66.4896500814379</v>
+        <v>68.2047249224854</v>
       </c>
       <c r="S50" s="11">
-        <v>47.296464759617</v>
+        <v>47.318528522633</v>
       </c>
       <c r="T50" s="11">
-        <v>53.8992206755311</v>
+        <v>54.3279708603017</v>
       </c>
       <c r="U50" s="11">
-        <v>47.9191834115049</v>
+        <v>48.2577803762078</v>
       </c>
       <c r="V50" s="11">
-        <v>64.6703855946832</v>
+        <v>64.82852344065719</v>
       </c>
       <c r="W50" s="11">
-        <v>47.7854382895327</v>
+        <v>49.0037042179383</v>
       </c>
       <c r="X50" s="11">
         <v>55.2218754064035</v>
       </c>
       <c r="Y50" s="11">
-        <v>68.9517669649301</v>
+        <v>67.1783874530049</v>
       </c>
       <c r="Z50" s="11">
-        <v>58.7481668926685</v>
+        <v>55.0304400919291</v>
       </c>
       <c r="AA50" s="11">
-        <v>79.1553670371917</v>
+        <v>79.3263348140806</v>
       </c>
       <c r="AB50" s="11">
-        <v>59.9146816869962</v>
+        <v>59.7559950119553</v>
       </c>
       <c r="AC50" s="11">
-        <v>52.7270586850322</v>
+        <v>52.6174502763274</v>
       </c>
     </row>
     <row r="51" ht="20.05" customHeight="1">
@@ -6106,82 +6108,82 @@
         <v>128</v>
       </c>
       <c r="D51" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E51" s="11">
-        <v>45.8397696452374</v>
+        <v>43.9095498278532</v>
       </c>
       <c r="F51" s="11">
-        <v>61.2350392875579</v>
+        <v>58.1822541500076</v>
       </c>
       <c r="G51" s="11">
-        <v>30.4445000029169</v>
+        <v>29.6368455056989</v>
       </c>
       <c r="H51" s="11">
-        <v>47.1435729333908</v>
+        <v>42.5493925927547</v>
       </c>
       <c r="I51" s="11">
-        <v>44.6920149958707</v>
+        <v>28.8504697052651</v>
       </c>
       <c r="J51" s="11">
-        <v>32.0156023518599</v>
+        <v>29.4434840979738</v>
       </c>
       <c r="K51" s="11">
-        <v>54.9717828522827</v>
+        <v>55.008725034230</v>
       </c>
       <c r="L51" s="11">
         <v>56.894891533550</v>
       </c>
       <c r="M51" s="11">
-        <v>50.7864456676801</v>
+        <v>55.182662829442</v>
       </c>
       <c r="N51" s="11">
-        <v>67.60105396741589</v>
+        <v>68.14703138365959</v>
       </c>
       <c r="O51" s="11">
-        <v>33.9718373679443</v>
+        <v>42.2182942752245</v>
       </c>
       <c r="P51" s="11">
-        <v>47.9232627487694</v>
+        <v>47.2138684166833</v>
       </c>
       <c r="Q51" s="11">
-        <v>43.6658042332517</v>
+        <v>41.8696576883959</v>
       </c>
       <c r="R51" s="11">
-        <v>8.97326494885548</v>
+        <v>5.00153031042984</v>
       </c>
       <c r="S51" s="11">
-        <v>78.3583435176479</v>
+        <v>78.73778506636199</v>
       </c>
       <c r="T51" s="11">
-        <v>62.3555159654597</v>
+        <v>64.2397410180988</v>
       </c>
       <c r="U51" s="11">
-        <v>50.1895334519129</v>
+        <v>52.9698157872719</v>
       </c>
       <c r="V51" s="11">
-        <v>86.3797541937973</v>
+        <v>88.4450193656274</v>
       </c>
       <c r="W51" s="11">
-        <v>62.9929322519328</v>
+        <v>65.6842849553002</v>
       </c>
       <c r="X51" s="11">
         <v>49.8598439641958</v>
       </c>
       <c r="Y51" s="11">
-        <v>36.596449021667</v>
+        <v>35.3947697339188</v>
       </c>
       <c r="Z51" s="11">
-        <v>37.0935242941419</v>
+        <v>38.4380447855126</v>
       </c>
       <c r="AA51" s="11">
-        <v>36.099373749192</v>
+        <v>32.351494682325</v>
       </c>
       <c r="AB51" s="11">
-        <v>47.5392564067928</v>
+        <v>47.1680561468045</v>
       </c>
       <c r="AC51" s="11">
-        <v>47.7312595777811</v>
+        <v>47.1909622817439</v>
       </c>
     </row>
     <row r="52" ht="20.05" customHeight="1">
@@ -6195,82 +6197,82 @@
         <v>130</v>
       </c>
       <c r="D52" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E52" s="11">
-        <v>48.1313233786054</v>
+        <v>49.2841111132716</v>
       </c>
       <c r="F52" s="11">
-        <v>74.81034343726979</v>
+        <v>74.1299765683178</v>
       </c>
       <c r="G52" s="11">
-        <v>21.452303319941</v>
+        <v>24.4382456582254</v>
       </c>
       <c r="H52" s="11">
-        <v>60.8723408276847</v>
+        <v>61.0018149274635</v>
       </c>
       <c r="I52" s="11">
-        <v>81.7235618121635</v>
+        <v>81.8113393373021</v>
       </c>
       <c r="J52" s="11">
-        <v>27.5343615214747</v>
+        <v>28.511590112494</v>
       </c>
       <c r="K52" s="11">
-        <v>56.5605960068139</v>
+        <v>56.0134862897711</v>
       </c>
       <c r="L52" s="11">
         <v>77.6708439702867</v>
       </c>
       <c r="M52" s="11">
-        <v>38.0900863646118</v>
+        <v>40.6145038595803</v>
       </c>
       <c r="N52" s="11">
-        <v>45.2858438041221</v>
+        <v>47.9291230313664</v>
       </c>
       <c r="O52" s="11">
-        <v>30.8943289251015</v>
+        <v>33.2998846877941</v>
       </c>
       <c r="P52" s="11">
-        <v>49.0312501903006</v>
+        <v>50.3001433001051</v>
       </c>
       <c r="Q52" s="11">
-        <v>66.29160780328959</v>
+        <v>66.9972077794219</v>
       </c>
       <c r="R52" s="11">
-        <v>46.8748488312062</v>
+        <v>50.2159559414741</v>
       </c>
       <c r="S52" s="11">
-        <v>85.70836677537309</v>
+        <v>83.77845961736971</v>
       </c>
       <c r="T52" s="11">
-        <v>72.40960075340379</v>
+        <v>72.3011019942664</v>
       </c>
       <c r="U52" s="11">
-        <v>71.5404127185306</v>
+        <v>71.57612589211929</v>
       </c>
       <c r="V52" s="11">
-        <v>80.80942067996391</v>
+        <v>79.41101151334961</v>
       </c>
       <c r="W52" s="11">
-        <v>49.6819145158817</v>
+        <v>50.6106154723574</v>
       </c>
       <c r="X52" s="11">
         <v>87.60665509923911</v>
       </c>
       <c r="Y52" s="11">
-        <v>72.71327485947469</v>
+        <v>73.3794445563227</v>
       </c>
       <c r="Z52" s="11">
-        <v>62.6140130518385</v>
+        <v>63.7161466972344</v>
       </c>
       <c r="AA52" s="11">
-        <v>82.812536667111</v>
+        <v>83.042742415411</v>
       </c>
       <c r="AB52" s="11">
-        <v>70.47149447205609</v>
+        <v>70.8925847766703</v>
       </c>
       <c r="AC52" s="11">
-        <v>59.7513723311783</v>
+        <v>60.5963640383877</v>
       </c>
     </row>
     <row r="53" ht="20.05" customHeight="1">
@@ -6284,82 +6286,82 @@
         <v>132</v>
       </c>
       <c r="D53" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E53" s="11">
-        <v>46.6639594926386</v>
+        <v>47.866017996916</v>
       </c>
       <c r="F53" s="11">
-        <v>58.0869403180398</v>
+        <v>57.7984603922527</v>
       </c>
       <c r="G53" s="11">
-        <v>35.2409786672373</v>
+        <v>37.9335756015794</v>
       </c>
       <c r="H53" s="11">
-        <v>47.3764721662617</v>
+        <v>46.7663741025012</v>
       </c>
       <c r="I53" s="11">
-        <v>42.7332973972794</v>
+        <v>41.4501886069439</v>
       </c>
       <c r="J53" s="11">
-        <v>43.5658566313112</v>
+        <v>44.5190246309869</v>
       </c>
       <c r="K53" s="11">
-        <v>58.5078037698944</v>
+        <v>56.3973523055124</v>
       </c>
       <c r="L53" s="11">
         <v>44.6989308665616</v>
       </c>
       <c r="M53" s="11">
-        <v>44.7102946578021</v>
+        <v>47.6911618047613</v>
       </c>
       <c r="N53" s="11">
-        <v>51.3100413756376</v>
+        <v>54.3453141497506</v>
       </c>
       <c r="O53" s="11">
-        <v>38.1105479399665</v>
+        <v>41.037009459772</v>
       </c>
       <c r="P53" s="11">
-        <v>46.2502421055674</v>
+        <v>47.4411846347262</v>
       </c>
       <c r="Q53" s="11">
-        <v>50.4028835596803</v>
+        <v>49.9193559848297</v>
       </c>
       <c r="R53" s="11">
-        <v>35.7043297680367</v>
+        <v>36.6640719445007</v>
       </c>
       <c r="S53" s="11">
-        <v>65.1014373513239</v>
+        <v>63.1746400251588</v>
       </c>
       <c r="T53" s="11">
-        <v>55.5259306002393</v>
+        <v>56.1111573271016</v>
       </c>
       <c r="U53" s="11">
-        <v>43.3456003284798</v>
+        <v>44.8790637781144</v>
       </c>
       <c r="V53" s="11">
-        <v>58.4320864538101</v>
+        <v>59.7903657768647</v>
       </c>
       <c r="W53" s="11">
-        <v>72.9594244356969</v>
+        <v>72.4085885704572</v>
       </c>
       <c r="X53" s="11">
         <v>47.3666111829702</v>
       </c>
       <c r="Y53" s="11">
-        <v>60.6211660650827</v>
+        <v>61.3782497008631</v>
       </c>
       <c r="Z53" s="11">
-        <v>71.22389525732549</v>
+        <v>73.16175950837059</v>
       </c>
       <c r="AA53" s="11">
-        <v>50.0184368728399</v>
+        <v>49.5947398933555</v>
       </c>
       <c r="AB53" s="11">
-        <v>55.5166600750007</v>
+        <v>55.8029210042648</v>
       </c>
       <c r="AC53" s="11">
-        <v>50.8834510902841</v>
+        <v>51.6220528194955</v>
       </c>
     </row>
     <row r="54" ht="20.05" customHeight="1">
@@ -6373,82 +6375,82 @@
         <v>134</v>
       </c>
       <c r="D54" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E54" s="11">
-        <v>40.1993497223311</v>
+        <v>41.6734114297054</v>
       </c>
       <c r="F54" s="11">
-        <v>49.7344388556635</v>
+        <v>48.437959408997</v>
       </c>
       <c r="G54" s="11">
-        <v>30.6642605889987</v>
+        <v>34.9088634504139</v>
       </c>
       <c r="H54" s="11">
-        <v>47.633822627512</v>
+        <v>47.0013163192121</v>
       </c>
       <c r="I54" s="11">
-        <v>29.5783004287407</v>
+        <v>28.2178575542371</v>
       </c>
       <c r="J54" s="11">
-        <v>82.7500773905459</v>
+        <v>82.8197563609119</v>
       </c>
       <c r="K54" s="11">
-        <v>38.3208830219988</v>
+        <v>37.0816216929368</v>
       </c>
       <c r="L54" s="11">
         <v>39.8860296687625</v>
       </c>
       <c r="M54" s="11">
-        <v>76.86507368308099</v>
+        <v>75.7706305600905</v>
       </c>
       <c r="N54" s="11">
-        <v>75.7310503689741</v>
+        <v>71.1418947285578</v>
       </c>
       <c r="O54" s="11">
-        <v>77.99909699718791</v>
+        <v>80.3993663916232</v>
       </c>
       <c r="P54" s="11">
-        <v>54.899415344308</v>
+        <v>54.815119436336</v>
       </c>
       <c r="Q54" s="11">
-        <v>64.33890299850999</v>
+        <v>63.3412482565274</v>
       </c>
       <c r="R54" s="11">
-        <v>84.3560801555336</v>
+        <v>84.690686563553</v>
       </c>
       <c r="S54" s="11">
-        <v>44.3217258414863</v>
+        <v>41.9918099495018</v>
       </c>
       <c r="T54" s="11">
-        <v>35.778363109358</v>
+        <v>36.1275089180703</v>
       </c>
       <c r="U54" s="11">
-        <v>29.5088571891523</v>
+        <v>30.5394988036847</v>
       </c>
       <c r="V54" s="11">
-        <v>9.48602238946955</v>
+        <v>10.9195867715352</v>
       </c>
       <c r="W54" s="11">
-        <v>73.1380314393666</v>
+        <v>72.07040867761791</v>
       </c>
       <c r="X54" s="11">
         <v>30.9805414194434</v>
       </c>
       <c r="Y54" s="11">
-        <v>13.7469892094608</v>
+        <v>13.4681074644862</v>
       </c>
       <c r="Z54" s="11">
-        <v>4.04539486536968</v>
+        <v>3.24835510509898</v>
       </c>
       <c r="AA54" s="11">
-        <v>23.448583553552</v>
+        <v>23.6878598238735</v>
       </c>
       <c r="AB54" s="11">
-        <v>37.9547517724429</v>
+        <v>37.6456215463613</v>
       </c>
       <c r="AC54" s="11">
-        <v>46.4270835583755</v>
+        <v>46.2303704913487</v>
       </c>
     </row>
     <row r="55" ht="20.05" customHeight="1">
@@ -6462,82 +6464,82 @@
         <v>136</v>
       </c>
       <c r="D55" s="11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E55" s="11">
-        <v>38.910979735644</v>
+        <v>37.1921707572692</v>
       </c>
       <c r="F55" s="11">
-        <v>47.538575060467</v>
+        <v>48.5805956918203</v>
       </c>
       <c r="G55" s="11">
-        <v>30.283384410821</v>
+        <v>25.8037458227181</v>
       </c>
       <c r="H55" s="11">
-        <v>56.4904448869648</v>
+        <v>60.5875927161509</v>
       </c>
       <c r="I55" s="11">
-        <v>40.2422347624567</v>
+        <v>46.4804193070661</v>
       </c>
       <c r="J55" s="11">
-        <v>45.3274559017006</v>
+        <v>48.1742694296874</v>
       </c>
       <c r="K55" s="11">
-        <v>54.0772821338823</v>
+        <v>61.3808753780306</v>
       </c>
       <c r="L55" s="11">
         <v>86.3148067498194</v>
       </c>
       <c r="M55" s="11">
-        <v>42.0959172413268</v>
+        <v>29.8319887968352</v>
       </c>
       <c r="N55" s="11">
-        <v>43.9955802683754</v>
+        <v>22.7110791749653</v>
       </c>
       <c r="O55" s="11">
-        <v>40.1962542142782</v>
+        <v>36.9528984187051</v>
       </c>
       <c r="P55" s="11">
-        <v>45.8324472879785</v>
+        <v>42.5372507567518</v>
       </c>
       <c r="Q55" s="11">
-        <v>75.2748988451481</v>
+        <v>76.7578558976921</v>
       </c>
       <c r="R55" s="11">
-        <v>83.5943136222284</v>
+        <v>82.9407691618956</v>
       </c>
       <c r="S55" s="11">
-        <v>66.9554840680679</v>
+        <v>70.5749426334885</v>
       </c>
       <c r="T55" s="11">
-        <v>62.0416950322658</v>
+        <v>62.0103815739189</v>
       </c>
       <c r="U55" s="11">
-        <v>34.5105174485838</v>
+        <v>31.5876447377495</v>
       </c>
       <c r="V55" s="11">
-        <v>68.8681187641787</v>
+        <v>70.8899457513739</v>
       </c>
       <c r="W55" s="11">
-        <v>57.4133110925436</v>
+        <v>58.1891029827953</v>
       </c>
       <c r="X55" s="11">
         <v>87.3748328237569</v>
       </c>
       <c r="Y55" s="11">
-        <v>70.87452720283559</v>
+        <v>65.6451938699918</v>
       </c>
       <c r="Z55" s="11">
-        <v>85.5408214233447</v>
+        <v>75.4454919808633</v>
       </c>
       <c r="AA55" s="11">
-        <v>56.2082329823265</v>
+        <v>55.8448957591204</v>
       </c>
       <c r="AB55" s="11">
-        <v>69.3970403600832</v>
+        <v>68.13781044720091</v>
       </c>
       <c r="AC55" s="11">
-        <v>57.6147438240308</v>
+        <v>55.3375306019763</v>
       </c>
     </row>
   </sheetData>
